--- a/tier-unification/sample-inputs/SAMPLE_Profiler-Export_AB2123-PFL_STANDARD_VC76.xlsx
+++ b/tier-unification/sample-inputs/SAMPLE_Profiler-Export_AB2123-PFL_STANDARD_VC76.xlsx
@@ -20,14 +20,14 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$A$1:$B$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Intake Answers'!$A$1:$D$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'SIMM Complexity'!$A$1:$K$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">Documents!$A$1:$E$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">Documents!$A$1:$E$60</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">Maps!$A$1:$K$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Engagement Matrix'!$A$1:$H$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Engagement Matrix'!$A$1:$H$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">Glossary!$A$1:$B$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'CA-PMF Templates'!$A$1:$B$49</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">Templates!$A$1:$B$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">Templates!$A$1:$B$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">Fields!$A$1:$B$89</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">Loops!$A$1:$B$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">Loops!$A$1:$B$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">Contradictions!$A$1:$B$5</definedName>
   </definedNames>
 </workbook>
@@ -1709,7 +1709,7 @@
         <v>V–C Read</v>
       </c>
       <c r="B5" s="8" t="str">
-        <v>Standard</v>
+        <v>Full</v>
       </c>
     </row>
     <row r="6">
@@ -1781,7 +1781,7 @@
         <v>Governance Tier</v>
       </c>
       <c r="B14" s="8" t="str">
-        <v>Tier 2</v>
+        <v>Tier 3</v>
       </c>
     </row>
     <row r="15">
@@ -1914,7 +1914,7 @@
     </row>
     <row r="31">
       <c r="A31" s="12" t="str">
-        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 1 of 8   ·   Generated Jul 2, 2026</v>
+        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 1 of 8   ·   Generated Jul 6, 2026</v>
       </c>
       <c r="B31" s="12" t="str">
         <v/>
@@ -2025,7 +2025,7 @@
         <v>vc_band</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>Standard</v>
+        <v>Full</v>
       </c>
     </row>
     <row r="12">
@@ -2033,7 +2033,7 @@
         <v>artifact_tier</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -2041,7 +2041,7 @@
         <v>governance_tier</v>
       </c>
       <c r="B13" s="2" t="str">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -2081,7 +2081,7 @@
         <v>version</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>v01.07</v>
+        <v>v01.09</v>
       </c>
     </row>
     <row r="19">
@@ -2089,7 +2089,7 @@
         <v>generated_on</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>2026-07-02</v>
+        <v>2026-07-06</v>
       </c>
     </row>
     <row r="20">
@@ -2662,7 +2662,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -3198,25 +3198,25 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="str">
-        <v>Product Vision</v>
+        <v>Project Governance Plan</v>
       </c>
       <c r="B15" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C15" s="2" t="str">
-        <v>Product Vision</v>
+        <v>Project Governance Plan</v>
       </c>
       <c r="D15" s="2" t="str">
         <v>PMO</v>
       </c>
       <c r="E15" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F15" s="2" t="str">
         <v>This phase</v>
       </c>
       <c r="G15" s="2" t="str">
-        <v>Q1 (delivery approach: agile)</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H15" s="2" t="str">
         <v/>
@@ -3236,25 +3236,25 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="str">
-        <v>Product Backlog</v>
+        <v>Governance / Steering-Committee Reporting</v>
       </c>
       <c r="B16" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C16" s="2" t="str">
-        <v>Product Backlog</v>
+        <v>Governance / Steering-Committee Reporting</v>
       </c>
       <c r="D16" s="2" t="str">
         <v>PMO</v>
       </c>
       <c r="E16" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F16" s="2" t="str">
-        <v>This phase</v>
+        <v>Ongoing</v>
       </c>
       <c r="G16" s="2" t="str">
-        <v>Q1 (delivery approach: agile)</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H16" s="2" t="str">
         <v/>
@@ -3274,25 +3274,25 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="str">
-        <v>Roadmap / Sprint Planning</v>
+        <v>Risk Management Plan</v>
       </c>
       <c r="B17" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C17" s="2" t="str">
-        <v>Roadmap / Sprint Planning</v>
+        <v>Risk Management Plan</v>
       </c>
       <c r="D17" s="2" t="str">
         <v>PMO</v>
       </c>
       <c r="E17" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F17" s="2" t="str">
         <v>This phase</v>
       </c>
       <c r="G17" s="2" t="str">
-        <v>Q1 (delivery approach: agile)</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H17" s="2" t="str">
         <v/>
@@ -3312,25 +3312,25 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="str">
-        <v>Rollback Plan</v>
+        <v>Quality Management Plan</v>
       </c>
       <c r="B18" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C18" s="2" t="str">
-        <v>Rollback Plan</v>
+        <v>Quality Management Plan</v>
       </c>
       <c r="D18" s="2" t="str">
-        <v>TARC → Development Team</v>
+        <v>PMO</v>
       </c>
       <c r="E18" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F18" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="G18" s="2" t="str">
-        <v>Q13 — new service</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H18" s="2" t="str">
         <v/>
@@ -3350,25 +3350,25 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="str">
-        <v>RFC / RRB</v>
+        <v>Communications Management Plan</v>
       </c>
       <c r="B19" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C19" s="2" t="str">
-        <v>RFC / RRB</v>
+        <v>Communications Management Plan</v>
       </c>
       <c r="D19" s="2" t="str">
-        <v>TARC → Development Team</v>
+        <v>PMO</v>
       </c>
       <c r="E19" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F19" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="G19" s="2" t="str">
-        <v>Q13 — new service</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H19" s="2" t="str">
         <v/>
@@ -3388,25 +3388,25 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="str">
-        <v>RRR Checklist</v>
+        <v>Change &amp; Schedule Management Plan</v>
       </c>
       <c r="B20" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C20" s="2" t="str">
-        <v>RRR Checklist</v>
+        <v>Change &amp; Schedule Management Plan</v>
       </c>
       <c r="D20" s="2" t="str">
-        <v>TARC → Development Team</v>
+        <v>PMO</v>
       </c>
       <c r="E20" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="G20" s="2" t="str">
-        <v>Q13 — new service</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H20" s="2" t="str">
         <v/>
@@ -3426,25 +3426,25 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="str">
-        <v>Hypercare / Production Readiness</v>
+        <v>Scope Management Plan</v>
       </c>
       <c r="B21" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C21" s="2" t="str">
-        <v>Hypercare / Production Readiness</v>
+        <v>Scope Management Plan</v>
       </c>
       <c r="D21" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="E21" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="G21" s="2" t="str">
-        <v>Q13 — new service</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H21" s="2" t="str">
         <v/>
@@ -3464,25 +3464,25 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="str">
-        <v>Privacy Impact Assessment (PIA)</v>
+        <v>Requirements Management Plan</v>
       </c>
       <c r="B22" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C22" s="2" t="str">
-        <v>Privacy Impact Assessment (PIA)</v>
+        <v>Requirements Management Plan</v>
       </c>
       <c r="D22" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="E22" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>Initiate</v>
+        <v>This phase</v>
       </c>
       <c r="G22" s="2" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H22" s="2" t="str">
         <v/>
@@ -3502,25 +3502,25 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="str">
-        <v>Business Impact Analysis (BIA)</v>
+        <v>Organization Management Plan</v>
       </c>
       <c r="B23" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C23" s="2" t="str">
-        <v>Business Impact Analysis (BIA)</v>
+        <v>Organization Management Plan</v>
       </c>
       <c r="D23" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="E23" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="G23" s="2" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H23" s="2" t="str">
         <v/>
@@ -3540,25 +3540,25 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="str">
-        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
+        <v>Procurement Management Plan</v>
       </c>
       <c r="B24" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C24" s="2" t="str">
-        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
+        <v>Procurement Management Plan</v>
       </c>
       <c r="D24" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="E24" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F24" s="2" t="str">
-        <v>Initiate</v>
+        <v>This phase</v>
       </c>
       <c r="G24" s="2" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H24" s="2" t="str">
         <v/>
@@ -3578,25 +3578,25 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="str">
-        <v>Risk Assessment</v>
+        <v>Cost Management Plan</v>
       </c>
       <c r="B25" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C25" s="2" t="str">
-        <v>Risk Assessment</v>
+        <v>Cost Management Plan</v>
       </c>
       <c r="D25" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="E25" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F25" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="G25" s="2" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H25" s="2" t="str">
         <v/>
@@ -3616,25 +3616,25 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="str">
-        <v>C&amp;A Package</v>
+        <v>Post-Implementation Review</v>
       </c>
       <c r="B26" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C26" s="2" t="str">
-        <v>C&amp;A Package</v>
+        <v>Post-Implementation Review</v>
       </c>
       <c r="D26" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="E26" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v>Execute</v>
+        <v>Close</v>
       </c>
       <c r="G26" s="2" t="str">
-        <v>Q28 — security review</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="H26" s="2" t="str">
         <v/>
@@ -3654,25 +3654,25 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="str">
-        <v>ISRP</v>
+        <v>Product Vision</v>
       </c>
       <c r="B27" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C27" s="2" t="str">
-        <v>ISRP</v>
+        <v>Product Vision</v>
       </c>
       <c r="D27" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="E27" s="2" t="str">
         <v/>
       </c>
       <c r="F27" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="G27" s="2" t="str">
-        <v>Q28 — security review</v>
+        <v>Q1 (delivery approach: agile)</v>
       </c>
       <c r="H27" s="2" t="str">
         <v/>
@@ -3692,25 +3692,25 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="str">
-        <v>SIEM / Logging Kickoff</v>
+        <v>Product Backlog</v>
       </c>
       <c r="B28" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C28" s="2" t="str">
-        <v>SIEM / Logging Kickoff</v>
+        <v>Product Backlog</v>
       </c>
       <c r="D28" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="E28" s="2" t="str">
         <v/>
       </c>
       <c r="F28" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="G28" s="2" t="str">
-        <v>Q28 — security review</v>
+        <v>Q1 (delivery approach: agile)</v>
       </c>
       <c r="H28" s="2" t="str">
         <v/>
@@ -3730,25 +3730,25 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="str">
-        <v>Vulnerability Scan &amp; Pen Test</v>
+        <v>Roadmap / Sprint Planning</v>
       </c>
       <c r="B29" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C29" s="2" t="str">
-        <v>Vulnerability Scan &amp; Pen Test</v>
+        <v>Roadmap / Sprint Planning</v>
       </c>
       <c r="D29" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="E29" s="2" t="str">
         <v/>
       </c>
       <c r="F29" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="G29" s="2" t="str">
-        <v>Q28 — security review</v>
+        <v>Q1 (delivery approach: agile)</v>
       </c>
       <c r="H29" s="2" t="str">
         <v/>
@@ -3768,25 +3768,25 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="str">
-        <v>Cloud Architecture Diagram</v>
+        <v>Rollback Plan</v>
       </c>
       <c r="B30" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C30" s="2" t="str">
-        <v>Cloud Architecture Diagram</v>
+        <v>Rollback Plan</v>
       </c>
       <c r="D30" s="2" t="str">
-        <v>TARC</v>
+        <v>TARC → Development Team</v>
       </c>
       <c r="E30" s="2" t="str">
         <v/>
       </c>
       <c r="F30" s="2" t="str">
-        <v>This phase</v>
+        <v>Execute</v>
       </c>
       <c r="G30" s="2" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q13 — new service</v>
       </c>
       <c r="H30" s="2" t="str">
         <v/>
@@ -3806,16 +3806,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="str">
-        <v>Cloud Documentation</v>
+        <v>RFC / RRB</v>
       </c>
       <c r="B31" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C31" s="2" t="str">
-        <v>Cloud Documentation</v>
+        <v>RFC / RRB</v>
       </c>
       <c r="D31" s="2" t="str">
-        <v>TARC</v>
+        <v>TARC → Development Team</v>
       </c>
       <c r="E31" s="2" t="str">
         <v/>
@@ -3824,7 +3824,7 @@
         <v>Execute</v>
       </c>
       <c r="G31" s="2" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q13 — new service</v>
       </c>
       <c r="H31" s="2" t="str">
         <v/>
@@ -3844,16 +3844,16 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="str">
-        <v>Cloud Review</v>
+        <v>RRR Checklist</v>
       </c>
       <c r="B32" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C32" s="2" t="str">
-        <v>Cloud Review</v>
+        <v>RRR Checklist</v>
       </c>
       <c r="D32" s="2" t="str">
-        <v>TARC</v>
+        <v>TARC → Development Team</v>
       </c>
       <c r="E32" s="2" t="str">
         <v/>
@@ -3862,7 +3862,7 @@
         <v>Execute</v>
       </c>
       <c r="G32" s="2" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q13 — new service</v>
       </c>
       <c r="H32" s="2" t="str">
         <v/>
@@ -3882,13 +3882,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="str">
-        <v>TARC</v>
+        <v>Hypercare / Production Readiness</v>
       </c>
       <c r="B33" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C33" s="2" t="str">
-        <v>TARC</v>
+        <v>Hypercare / Production Readiness</v>
       </c>
       <c r="D33" s="2" t="str">
         <v>TARC</v>
@@ -3900,7 +3900,7 @@
         <v>Execute</v>
       </c>
       <c r="G33" s="2" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q13 — new service</v>
       </c>
       <c r="H33" s="2" t="str">
         <v/>
@@ -3920,25 +3920,25 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="str">
-        <v>Vendor SOW &amp; Contract Oversight</v>
+        <v>Privacy Impact Assessment (PIA)</v>
       </c>
       <c r="B34" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C34" s="2" t="str">
-        <v>Vendor SOW &amp; Contract Oversight</v>
+        <v>Privacy Impact Assessment (PIA)</v>
       </c>
       <c r="D34" s="2" t="str">
-        <v>TARC → TGD — Procurement</v>
+        <v>TARC</v>
       </c>
       <c r="E34" s="2" t="str">
         <v/>
       </c>
       <c r="F34" s="2" t="str">
-        <v>This phase</v>
+        <v>Initiate</v>
       </c>
       <c r="G34" s="2" t="str">
-        <v>Q18 — vendor-delivered</v>
+        <v>Q23 — sensitive data</v>
       </c>
       <c r="H34" s="2" t="str">
         <v/>
@@ -3958,13 +3958,13 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="str">
-        <v>Test Strategy</v>
+        <v>Business Impact Analysis (BIA)</v>
       </c>
       <c r="B35" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C35" s="2" t="str">
-        <v>Test Strategy</v>
+        <v>Business Impact Analysis (BIA)</v>
       </c>
       <c r="D35" s="2" t="str">
         <v>TARC</v>
@@ -3973,10 +3973,10 @@
         <v/>
       </c>
       <c r="F35" s="2" t="str">
-        <v>This phase</v>
+        <v>Execute</v>
       </c>
       <c r="G35" s="2" t="str">
-        <v>Q30 — testing</v>
+        <v>Q23 — sensitive data</v>
       </c>
       <c r="H35" s="2" t="str">
         <v/>
@@ -3996,13 +3996,13 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="str">
-        <v>Operations, Support &amp; M&amp;O Plan</v>
+        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
       </c>
       <c r="B36" s="2" t="str">
         <v>documents</v>
       </c>
       <c r="C36" s="2" t="str">
-        <v>Operations, Support &amp; M&amp;O Plan</v>
+        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
       </c>
       <c r="D36" s="2" t="str">
         <v>TARC</v>
@@ -4011,10 +4011,10 @@
         <v/>
       </c>
       <c r="F36" s="2" t="str">
-        <v>Execute</v>
+        <v>Initiate</v>
       </c>
       <c r="G36" s="2" t="str">
-        <v>Q31 — support / M&amp;O</v>
+        <v>Q23 — sensitive data</v>
       </c>
       <c r="H36" s="2" t="str">
         <v/>
@@ -4034,31 +4034,31 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="str">
-        <v>Project Charter</v>
+        <v>Risk Assessment</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>risks</v>
+        <v>documents</v>
       </c>
       <c r="C37" s="2" t="str">
-        <v/>
+        <v>Risk Assessment</v>
       </c>
       <c r="D37" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E37" s="2" t="str">
         <v/>
       </c>
       <c r="F37" s="2" t="str">
-        <v/>
+        <v>Execute</v>
       </c>
       <c r="G37" s="2" t="str">
-        <v/>
+        <v>Q23 — sensitive data</v>
       </c>
       <c r="H37" s="2" t="str">
-        <v>[REVIEW] External / public-facing impact raises reputational and accessibility stakes.</v>
+        <v/>
       </c>
       <c r="I37" s="2" t="str">
-        <v>Plan accessibility (508) review, comms, and a measured external rollout.</v>
+        <v/>
       </c>
       <c r="J37" s="2" t="str">
         <v/>
@@ -4072,31 +4072,31 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="str">
-        <v>Project Charter</v>
+        <v>C&amp;A Package</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>risks</v>
+        <v>documents</v>
       </c>
       <c r="C38" s="2" t="str">
-        <v/>
+        <v>C&amp;A Package</v>
       </c>
       <c r="D38" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E38" s="2" t="str">
         <v/>
       </c>
       <c r="F38" s="2" t="str">
-        <v/>
+        <v>Execute</v>
       </c>
       <c r="G38" s="2" t="str">
-        <v/>
+        <v>Q28 — security review</v>
       </c>
       <c r="H38" s="2" t="str">
-        <v>[REVIEW] New or changed production service introduces deployment and stability risk.</v>
+        <v/>
       </c>
       <c r="I38" s="2" t="str">
-        <v>Plan staged rollout, defined rollback, and production-readiness review (RRR) before go-live.</v>
+        <v/>
       </c>
       <c r="J38" s="2" t="str">
         <v/>
@@ -4110,31 +4110,31 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="str">
-        <v>Project Charter</v>
+        <v>ISRP</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>risks</v>
+        <v>documents</v>
       </c>
       <c r="C39" s="2" t="str">
-        <v/>
+        <v>ISRP</v>
       </c>
       <c r="D39" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E39" s="2" t="str">
         <v/>
       </c>
       <c r="F39" s="2" t="str">
-        <v/>
+        <v>Execute</v>
       </c>
       <c r="G39" s="2" t="str">
-        <v/>
+        <v>Q28 — security review</v>
       </c>
       <c r="H39" s="2" t="str">
-        <v>[REVIEW] Vendor-delivered scope creates dependency, procurement, and SOW risk.</v>
+        <v/>
       </c>
       <c r="I39" s="2" t="str">
-        <v>Route through TGD Procurement; define SOW, acceptance criteria, and milestones.</v>
+        <v/>
       </c>
       <c r="J39" s="2" t="str">
         <v/>
@@ -4148,31 +4148,31 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="str">
-        <v>Project Charter</v>
+        <v>SIEM / Logging Kickoff</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>risks</v>
+        <v>documents</v>
       </c>
       <c r="C40" s="2" t="str">
-        <v/>
+        <v>SIEM / Logging Kickoff</v>
       </c>
       <c r="D40" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E40" s="2" t="str">
         <v/>
       </c>
       <c r="F40" s="2" t="str">
-        <v/>
+        <v>Execute</v>
       </c>
       <c r="G40" s="2" t="str">
-        <v/>
+        <v>Q28 — security review</v>
       </c>
       <c r="H40" s="2" t="str">
-        <v>[REVIEW] Project handles sensitive/PII data — privacy and data-protection exposure.</v>
+        <v/>
       </c>
       <c r="I40" s="2" t="str">
-        <v>Complete privacy threshold assessment; apply data-handling, encryption, and access controls.</v>
+        <v/>
       </c>
       <c r="J40" s="2" t="str">
         <v/>
@@ -4186,31 +4186,31 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="str">
-        <v>Project Charter</v>
+        <v>Vulnerability Scan &amp; Pen Test</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>risks</v>
+        <v>documents</v>
       </c>
       <c r="C41" s="2" t="str">
-        <v/>
+        <v>Vulnerability Scan &amp; Pen Test</v>
       </c>
       <c r="D41" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E41" s="2" t="str">
         <v/>
       </c>
       <c r="F41" s="2" t="str">
-        <v/>
+        <v>Execute</v>
       </c>
       <c r="G41" s="2" t="str">
-        <v/>
+        <v>Q28 — security review</v>
       </c>
       <c r="H41" s="2" t="str">
-        <v>[REVIEW] Heavy cross-team dependencies may delay the critical path.</v>
+        <v/>
       </c>
       <c r="I41" s="2" t="str">
-        <v>Map dependencies in the RAID log; secure commitments from owning teams early.</v>
+        <v/>
       </c>
       <c r="J41" s="2" t="str">
         <v/>
@@ -4224,31 +4224,31 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="str">
-        <v>Project Charter</v>
+        <v>Cloud Architecture Diagram</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>risks</v>
+        <v>documents</v>
       </c>
       <c r="C42" s="2" t="str">
-        <v/>
+        <v>Cloud Architecture Diagram</v>
       </c>
       <c r="D42" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E42" s="2" t="str">
         <v/>
       </c>
       <c r="F42" s="2" t="str">
-        <v/>
+        <v>This phase</v>
       </c>
       <c r="G42" s="2" t="str">
-        <v/>
+        <v>Q29 — cloud / infra</v>
       </c>
       <c r="H42" s="2" t="str">
-        <v>[REVIEW] Security review required — potential vulnerabilities or compliance gaps.</v>
+        <v/>
       </c>
       <c r="I42" s="2" t="str">
-        <v>Engage Cyber Security for assessment; remediate findings before each gate.</v>
+        <v/>
       </c>
       <c r="J42" s="2" t="str">
         <v/>
@@ -4262,31 +4262,31 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="str">
-        <v>Project Charter</v>
+        <v>Cloud Documentation</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>risks</v>
+        <v>documents</v>
       </c>
       <c r="C43" s="2" t="str">
-        <v/>
+        <v>Cloud Documentation</v>
       </c>
       <c r="D43" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E43" s="2" t="str">
         <v/>
       </c>
       <c r="F43" s="2" t="str">
-        <v/>
+        <v>Execute</v>
       </c>
       <c r="G43" s="2" t="str">
-        <v/>
+        <v>Q29 — cloud / infra</v>
       </c>
       <c r="H43" s="2" t="str">
-        <v>[REVIEW] Cloud / infrastructure dependency introduces availability and configuration risk.</v>
+        <v/>
       </c>
       <c r="I43" s="2" t="str">
-        <v>Confirm Infrastructure Services capacity, IAM, and DR posture during planning.</v>
+        <v/>
       </c>
       <c r="J43" s="2" t="str">
         <v/>
@@ -4300,31 +4300,31 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="str">
-        <v>Project Charter</v>
+        <v>Cloud Review</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>risks</v>
+        <v>documents</v>
       </c>
       <c r="C44" s="2" t="str">
-        <v/>
+        <v>Cloud Review</v>
       </c>
       <c r="D44" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E44" s="2" t="str">
         <v/>
       </c>
       <c r="F44" s="2" t="str">
-        <v/>
+        <v>Execute</v>
       </c>
       <c r="G44" s="2" t="str">
-        <v/>
+        <v>Q29 — cloud / infra</v>
       </c>
       <c r="H44" s="2" t="str">
-        <v>[REVIEW] Elevated criticality (High) — failure impact is significant.</v>
+        <v/>
       </c>
       <c r="I44" s="2" t="str">
-        <v>Increase oversight cadence and escalation; align governance to the criticality zone.</v>
+        <v/>
       </c>
       <c r="J44" s="2" t="str">
         <v/>
@@ -4338,25 +4338,25 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="str">
-        <v>Project Charter</v>
+        <v>TARC</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>milestones</v>
+        <v>documents</v>
       </c>
       <c r="C45" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="D45" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E45" s="2" t="str">
         <v/>
       </c>
       <c r="F45" s="2" t="str">
-        <v/>
+        <v>Execute</v>
       </c>
       <c r="G45" s="2" t="str">
-        <v/>
+        <v>Q29 — cloud / infra</v>
       </c>
       <c r="H45" s="2" t="str">
         <v/>
@@ -4365,10 +4365,10 @@
         <v/>
       </c>
       <c r="J45" s="2" t="str">
-        <v>[REVIEW] Concept phase complete</v>
+        <v/>
       </c>
       <c r="K45" s="2" t="str">
-        <v>Concept</v>
+        <v/>
       </c>
       <c r="L45" s="2" t="str">
         <v/>
@@ -4376,25 +4376,25 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="str">
-        <v>Project Charter</v>
+        <v>Vendor SOW &amp; Contract Oversight</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>milestones</v>
+        <v>documents</v>
       </c>
       <c r="C46" s="2" t="str">
-        <v/>
+        <v>Vendor SOW &amp; Contract Oversight</v>
       </c>
       <c r="D46" s="2" t="str">
-        <v/>
+        <v>TARC → TGD — Procurement</v>
       </c>
       <c r="E46" s="2" t="str">
         <v/>
       </c>
       <c r="F46" s="2" t="str">
-        <v/>
+        <v>This phase</v>
       </c>
       <c r="G46" s="2" t="str">
-        <v/>
+        <v>Q18 — vendor-delivered</v>
       </c>
       <c r="H46" s="2" t="str">
         <v/>
@@ -4403,10 +4403,10 @@
         <v/>
       </c>
       <c r="J46" s="2" t="str">
-        <v>[REVIEW] Initiate phase complete</v>
+        <v/>
       </c>
       <c r="K46" s="2" t="str">
-        <v>Initiate</v>
+        <v/>
       </c>
       <c r="L46" s="2" t="str">
         <v/>
@@ -4414,25 +4414,25 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="str">
-        <v>Project Charter</v>
+        <v>Test Strategy</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>milestones</v>
+        <v>documents</v>
       </c>
       <c r="C47" s="2" t="str">
-        <v/>
+        <v>Test Strategy</v>
       </c>
       <c r="D47" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E47" s="2" t="str">
         <v/>
       </c>
       <c r="F47" s="2" t="str">
-        <v/>
+        <v>This phase</v>
       </c>
       <c r="G47" s="2" t="str">
-        <v/>
+        <v>Q30 — testing</v>
       </c>
       <c r="H47" s="2" t="str">
         <v/>
@@ -4441,10 +4441,10 @@
         <v/>
       </c>
       <c r="J47" s="2" t="str">
-        <v>[REVIEW] Plan phase complete</v>
+        <v/>
       </c>
       <c r="K47" s="2" t="str">
-        <v>Plan</v>
+        <v/>
       </c>
       <c r="L47" s="2" t="str">
         <v/>
@@ -4452,25 +4452,25 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="str">
-        <v>Project Charter</v>
+        <v>Operations, Support &amp; M&amp;O Plan</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>milestones</v>
+        <v>documents</v>
       </c>
       <c r="C48" s="2" t="str">
-        <v/>
+        <v>Operations, Support &amp; M&amp;O Plan</v>
       </c>
       <c r="D48" s="2" t="str">
-        <v/>
+        <v>TARC</v>
       </c>
       <c r="E48" s="2" t="str">
         <v/>
       </c>
       <c r="F48" s="2" t="str">
-        <v/>
+        <v>Execute</v>
       </c>
       <c r="G48" s="2" t="str">
-        <v/>
+        <v>Q31 — support / M&amp;O</v>
       </c>
       <c r="H48" s="2" t="str">
         <v/>
@@ -4479,10 +4479,10 @@
         <v/>
       </c>
       <c r="J48" s="2" t="str">
-        <v>[REVIEW] Execute phase complete</v>
+        <v/>
       </c>
       <c r="K48" s="2" t="str">
-        <v>Execute</v>
+        <v/>
       </c>
       <c r="L48" s="2" t="str">
         <v/>
@@ -4493,43 +4493,499 @@
         <v>Project Charter</v>
       </c>
       <c r="B49" s="2" t="str">
+        <v>risks</v>
+      </c>
+      <c r="C49" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D49" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E49" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F49" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H49" s="2" t="str">
+        <v>[REVIEW] External / public-facing impact raises reputational and accessibility stakes.</v>
+      </c>
+      <c r="I49" s="2" t="str">
+        <v>Plan accessibility (508) review, comms, and a measured external rollout.</v>
+      </c>
+      <c r="J49" s="2" t="str">
+        <v/>
+      </c>
+      <c r="K49" s="2" t="str">
+        <v/>
+      </c>
+      <c r="L49" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B50" s="2" t="str">
+        <v>risks</v>
+      </c>
+      <c r="C50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H50" s="2" t="str">
+        <v>[REVIEW] New or changed production service introduces deployment and stability risk.</v>
+      </c>
+      <c r="I50" s="2" t="str">
+        <v>Plan staged rollout, defined rollback, and production-readiness review (RRR) before go-live.</v>
+      </c>
+      <c r="J50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="K50" s="2" t="str">
+        <v/>
+      </c>
+      <c r="L50" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B51" s="2" t="str">
+        <v>risks</v>
+      </c>
+      <c r="C51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H51" s="2" t="str">
+        <v>[REVIEW] Vendor-delivered scope creates dependency, procurement, and SOW risk.</v>
+      </c>
+      <c r="I51" s="2" t="str">
+        <v>Route through TGD Procurement; define SOW, acceptance criteria, and milestones.</v>
+      </c>
+      <c r="J51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="K51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="L51" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B52" s="2" t="str">
+        <v>risks</v>
+      </c>
+      <c r="C52" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D52" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E52" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F52" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H52" s="2" t="str">
+        <v>[REVIEW] Project handles sensitive/PII data — privacy and data-protection exposure.</v>
+      </c>
+      <c r="I52" s="2" t="str">
+        <v>Complete privacy threshold assessment; apply data-handling, encryption, and access controls.</v>
+      </c>
+      <c r="J52" s="2" t="str">
+        <v/>
+      </c>
+      <c r="K52" s="2" t="str">
+        <v/>
+      </c>
+      <c r="L52" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B53" s="2" t="str">
+        <v>risks</v>
+      </c>
+      <c r="C53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H53" s="2" t="str">
+        <v>[REVIEW] Heavy cross-team dependencies may delay the critical path.</v>
+      </c>
+      <c r="I53" s="2" t="str">
+        <v>Map dependencies in the RAID log; secure commitments from owning teams early.</v>
+      </c>
+      <c r="J53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="K53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="L53" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B54" s="2" t="str">
+        <v>risks</v>
+      </c>
+      <c r="C54" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D54" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E54" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F54" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H54" s="2" t="str">
+        <v>[REVIEW] Security review required — potential vulnerabilities or compliance gaps.</v>
+      </c>
+      <c r="I54" s="2" t="str">
+        <v>Engage Cyber Security for assessment; remediate findings before each gate.</v>
+      </c>
+      <c r="J54" s="2" t="str">
+        <v/>
+      </c>
+      <c r="K54" s="2" t="str">
+        <v/>
+      </c>
+      <c r="L54" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B55" s="2" t="str">
+        <v>risks</v>
+      </c>
+      <c r="C55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H55" s="2" t="str">
+        <v>[REVIEW] Cloud / infrastructure dependency introduces availability and configuration risk.</v>
+      </c>
+      <c r="I55" s="2" t="str">
+        <v>Confirm Infrastructure Services capacity, IAM, and DR posture during planning.</v>
+      </c>
+      <c r="J55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="K55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="L55" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B56" s="2" t="str">
+        <v>risks</v>
+      </c>
+      <c r="C56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H56" s="2" t="str">
+        <v>[REVIEW] Elevated criticality (High) — failure impact is significant.</v>
+      </c>
+      <c r="I56" s="2" t="str">
+        <v>Increase oversight cadence and escalation; align governance to the criticality zone.</v>
+      </c>
+      <c r="J56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="K56" s="2" t="str">
+        <v/>
+      </c>
+      <c r="L56" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B57" s="2" t="str">
         <v>milestones</v>
       </c>
-      <c r="C49" s="2" t="str">
-        <v/>
-      </c>
-      <c r="D49" s="2" t="str">
-        <v/>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
-      </c>
-      <c r="F49" s="2" t="str">
-        <v/>
-      </c>
-      <c r="G49" s="2" t="str">
-        <v/>
-      </c>
-      <c r="H49" s="2" t="str">
-        <v/>
-      </c>
-      <c r="I49" s="2" t="str">
-        <v/>
-      </c>
-      <c r="J49" s="2" t="str">
+      <c r="C57" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D57" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E57" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F57" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H57" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I57" s="2" t="str">
+        <v/>
+      </c>
+      <c r="J57" s="2" t="str">
+        <v>[REVIEW] Concept phase complete</v>
+      </c>
+      <c r="K57" s="2" t="str">
+        <v>Concept</v>
+      </c>
+      <c r="L57" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B58" s="2" t="str">
+        <v>milestones</v>
+      </c>
+      <c r="C58" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D58" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E58" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F58" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H58" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I58" s="2" t="str">
+        <v/>
+      </c>
+      <c r="J58" s="2" t="str">
+        <v>[REVIEW] Initiate phase complete</v>
+      </c>
+      <c r="K58" s="2" t="str">
+        <v>Initiate</v>
+      </c>
+      <c r="L58" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B59" s="2" t="str">
+        <v>milestones</v>
+      </c>
+      <c r="C59" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D59" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E59" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F59" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H59" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I59" s="2" t="str">
+        <v/>
+      </c>
+      <c r="J59" s="2" t="str">
+        <v>[REVIEW] Plan phase complete</v>
+      </c>
+      <c r="K59" s="2" t="str">
+        <v>Plan</v>
+      </c>
+      <c r="L59" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B60" s="2" t="str">
+        <v>milestones</v>
+      </c>
+      <c r="C60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I60" s="2" t="str">
+        <v/>
+      </c>
+      <c r="J60" s="2" t="str">
+        <v>[REVIEW] Execute phase complete</v>
+      </c>
+      <c r="K60" s="2" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="L60" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="str">
+        <v>Project Charter</v>
+      </c>
+      <c r="B61" s="2" t="str">
+        <v>milestones</v>
+      </c>
+      <c r="C61" s="2" t="str">
+        <v/>
+      </c>
+      <c r="D61" s="2" t="str">
+        <v/>
+      </c>
+      <c r="E61" s="2" t="str">
+        <v/>
+      </c>
+      <c r="F61" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str">
+        <v/>
+      </c>
+      <c r="H61" s="2" t="str">
+        <v/>
+      </c>
+      <c r="I61" s="2" t="str">
+        <v/>
+      </c>
+      <c r="J61" s="2" t="str">
         <v>[REVIEW] Close phase complete</v>
       </c>
-      <c r="K49" s="2" t="str">
+      <c r="K61" s="2" t="str">
         <v>Close</v>
       </c>
-      <c r="L49" s="2" t="str">
+      <c r="L61" s="2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5120,7 +5576,7 @@
     </row>
     <row r="35">
       <c r="A35" s="12" t="str">
-        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 2 of 8   ·   Generated Jul 2, 2026</v>
+        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 2 of 8   ·   Generated Jul 6, 2026</v>
       </c>
       <c r="B35" s="12" t="str">
         <v/>
@@ -5968,7 +6424,7 @@
       </c>
       <c r="K23" s="8" t="str">
         <f>IF(K22&gt;=80,"Full",IF(AND(K21&lt;60,((E22+E23)/2)&lt;2.5),"Mini","Standard"))</f>
-        <v>Standard</v>
+        <v>Full</v>
       </c>
     </row>
   </sheetData>
@@ -5991,7 +6447,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E60"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
@@ -6223,7 +6679,7 @@
     </row>
     <row r="14">
       <c r="A14" s="17" t="str">
-        <v>Product Vision</v>
+        <v>Risk Management Plan</v>
       </c>
       <c r="B14" s="31" t="str">
         <v>PMO</v>
@@ -6232,15 +6688,15 @@
         <v>This phase</v>
       </c>
       <c r="D14" s="26" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="E14" s="17" t="str">
-        <v>Q1 (delivery approach: agile)</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="str">
-        <v>Product Backlog</v>
+        <v>Quality Management Plan</v>
       </c>
       <c r="B15" s="31" t="str">
         <v>PMO</v>
@@ -6249,15 +6705,15 @@
         <v>This phase</v>
       </c>
       <c r="D15" s="22" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="E15" s="11" t="str">
-        <v>Q1 (delivery approach: agile)</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="str">
-        <v>Roadmap / Sprint Planning</v>
+        <v>Communications Management Plan</v>
       </c>
       <c r="B16" s="31" t="str">
         <v>PMO</v>
@@ -6266,236 +6722,236 @@
         <v>This phase</v>
       </c>
       <c r="D16" s="26" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="E16" s="17" t="str">
-        <v>Q1 (delivery approach: agile)</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="str">
-        <v>Cloud Architecture Diagram</v>
-      </c>
-      <c r="B17" s="30" t="str">
-        <v>TARC</v>
+        <v>Change &amp; Schedule Management Plan</v>
+      </c>
+      <c r="B17" s="31" t="str">
+        <v>PMO</v>
       </c>
       <c r="C17" s="11" t="str">
         <v>This phase</v>
       </c>
       <c r="D17" s="22" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="E17" s="11" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="17" t="str">
-        <v>Vendor SOW &amp; Contract Oversight</v>
-      </c>
-      <c r="B18" s="30" t="str">
-        <v>TARC → TGD — Procurement</v>
+        <v>Scope Management Plan</v>
+      </c>
+      <c r="B18" s="31" t="str">
+        <v>PMO</v>
       </c>
       <c r="C18" s="17" t="str">
         <v>This phase</v>
       </c>
       <c r="D18" s="26" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="E18" s="17" t="str">
-        <v>Q18 — vendor-delivered</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="str">
-        <v>Security &amp; Risk</v>
-      </c>
-      <c r="B19" s="29" t="str">
-        <v/>
-      </c>
-      <c r="C19" s="29" t="str">
-        <v/>
-      </c>
-      <c r="D19" s="29" t="str">
-        <v/>
-      </c>
-      <c r="E19" s="29" t="str">
-        <v/>
+      <c r="A19" s="11" t="str">
+        <v>Requirements Management Plan</v>
+      </c>
+      <c r="B19" s="31" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="C19" s="11" t="str">
+        <v>This phase</v>
+      </c>
+      <c r="D19" s="22" t="str">
+        <v>T3</v>
+      </c>
+      <c r="E19" s="11" t="str">
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="str">
-        <v>Privacy Impact Assessment (PIA)</v>
-      </c>
-      <c r="B20" s="30" t="str">
-        <v>TARC</v>
+        <v>Organization Management Plan</v>
+      </c>
+      <c r="B20" s="31" t="str">
+        <v>PMO</v>
       </c>
       <c r="C20" s="17" t="str">
-        <v>Initiate</v>
+        <v>This phase</v>
       </c>
       <c r="D20" s="26" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="E20" s="17" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="str">
-        <v>Business Impact Analysis (BIA)</v>
-      </c>
-      <c r="B21" s="30" t="str">
-        <v>TARC</v>
+        <v>Procurement Management Plan</v>
+      </c>
+      <c r="B21" s="31" t="str">
+        <v>PMO</v>
       </c>
       <c r="C21" s="11" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="D21" s="22" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="E21" s="11" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="17" t="str">
-        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
-      </c>
-      <c r="B22" s="30" t="str">
-        <v>TARC</v>
+        <v>Cost Management Plan</v>
+      </c>
+      <c r="B22" s="31" t="str">
+        <v>PMO</v>
       </c>
       <c r="C22" s="17" t="str">
-        <v>Initiate</v>
+        <v>This phase</v>
       </c>
       <c r="D22" s="26" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="E22" s="17" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="str">
-        <v>Risk Assessment</v>
-      </c>
-      <c r="B23" s="30" t="str">
-        <v>TARC</v>
+        <v>Product Vision</v>
+      </c>
+      <c r="B23" s="31" t="str">
+        <v>PMO</v>
       </c>
       <c r="C23" s="11" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="D23" s="22" t="str">
         <v/>
       </c>
       <c r="E23" s="11" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Q1 (delivery approach: agile)</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="17" t="str">
-        <v>C&amp;A Package</v>
-      </c>
-      <c r="B24" s="30" t="str">
-        <v>TARC</v>
+        <v>Product Backlog</v>
+      </c>
+      <c r="B24" s="31" t="str">
+        <v>PMO</v>
       </c>
       <c r="C24" s="17" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="D24" s="26" t="str">
         <v/>
       </c>
       <c r="E24" s="17" t="str">
-        <v>Q28 — security review</v>
+        <v>Q1 (delivery approach: agile)</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="str">
-        <v>ISRP</v>
-      </c>
-      <c r="B25" s="30" t="str">
-        <v>TARC</v>
+        <v>Roadmap / Sprint Planning</v>
+      </c>
+      <c r="B25" s="31" t="str">
+        <v>PMO</v>
       </c>
       <c r="C25" s="11" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="D25" s="22" t="str">
         <v/>
       </c>
       <c r="E25" s="11" t="str">
-        <v>Q28 — security review</v>
+        <v>Q1 (delivery approach: agile)</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="str">
-        <v>SIEM / Logging Kickoff</v>
+        <v>Cloud Architecture Diagram</v>
       </c>
       <c r="B26" s="30" t="str">
         <v>TARC</v>
       </c>
       <c r="C26" s="17" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="D26" s="26" t="str">
         <v/>
       </c>
       <c r="E26" s="17" t="str">
-        <v>Q28 — security review</v>
+        <v>Q29 — cloud / infra</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="str">
-        <v>Vulnerability Scan &amp; Pen Test</v>
+        <v>Vendor SOW &amp; Contract Oversight</v>
       </c>
       <c r="B27" s="30" t="str">
-        <v>TARC</v>
+        <v>TARC → TGD — Procurement</v>
       </c>
       <c r="C27" s="11" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="D27" s="22" t="str">
         <v/>
       </c>
       <c r="E27" s="11" t="str">
-        <v>Q28 — security review</v>
+        <v>Q18 — vendor-delivered</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="str">
-        <v>Cloud Documentation</v>
-      </c>
-      <c r="B28" s="30" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="C28" s="17" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D28" s="26" t="str">
-        <v/>
-      </c>
-      <c r="E28" s="17" t="str">
-        <v>Q29 — cloud / infra</v>
+      <c r="A28" s="29" t="str">
+        <v>Security &amp; Risk</v>
+      </c>
+      <c r="B28" s="29" t="str">
+        <v/>
+      </c>
+      <c r="C28" s="29" t="str">
+        <v/>
+      </c>
+      <c r="D28" s="29" t="str">
+        <v/>
+      </c>
+      <c r="E28" s="29" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="str">
-        <v>Cloud Review</v>
+        <v>Privacy Impact Assessment (PIA)</v>
       </c>
       <c r="B29" s="30" t="str">
         <v>TARC</v>
       </c>
       <c r="C29" s="11" t="str">
-        <v>Execute</v>
+        <v>Initiate</v>
       </c>
       <c r="D29" s="22" t="str">
         <v/>
       </c>
       <c r="E29" s="11" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q23 — sensitive data</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="17" t="str">
-        <v>TARC</v>
+        <v>Business Impact Analysis (BIA)</v>
       </c>
       <c r="B30" s="30" t="str">
         <v>TARC</v>
@@ -6507,32 +6963,32 @@
         <v/>
       </c>
       <c r="E30" s="17" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q23 — sensitive data</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="str">
-        <v>Release &amp; Production</v>
-      </c>
-      <c r="B31" s="29" t="str">
-        <v/>
-      </c>
-      <c r="C31" s="29" t="str">
-        <v/>
-      </c>
-      <c r="D31" s="29" t="str">
-        <v/>
-      </c>
-      <c r="E31" s="29" t="str">
-        <v/>
+      <c r="A31" s="11" t="str">
+        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
+      </c>
+      <c r="B31" s="30" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="C31" s="11" t="str">
+        <v>Initiate</v>
+      </c>
+      <c r="D31" s="22" t="str">
+        <v/>
+      </c>
+      <c r="E31" s="11" t="str">
+        <v>Q23 — sensitive data</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="str">
-        <v>Implementation Plan</v>
+        <v>Risk Assessment</v>
       </c>
       <c r="B32" s="30" t="str">
-        <v>TARC → Development Team</v>
+        <v>TARC</v>
       </c>
       <c r="C32" s="17" t="str">
         <v>Execute</v>
@@ -6541,15 +6997,15 @@
         <v/>
       </c>
       <c r="E32" s="17" t="str">
-        <v>Baseline — every project</v>
+        <v>Q23 — sensitive data</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="str">
-        <v>Rollback Plan</v>
+        <v>C&amp;A Package</v>
       </c>
       <c r="B33" s="30" t="str">
-        <v>TARC → Development Team</v>
+        <v>TARC</v>
       </c>
       <c r="C33" s="11" t="str">
         <v>Execute</v>
@@ -6558,15 +7014,15 @@
         <v/>
       </c>
       <c r="E33" s="11" t="str">
-        <v>Q13 — new service</v>
+        <v>Q28 — security review</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="17" t="str">
-        <v>RFC / RRB</v>
+        <v>ISRP</v>
       </c>
       <c r="B34" s="30" t="str">
-        <v>TARC → Development Team</v>
+        <v>TARC</v>
       </c>
       <c r="C34" s="17" t="str">
         <v>Execute</v>
@@ -6575,15 +7031,15 @@
         <v/>
       </c>
       <c r="E34" s="17" t="str">
-        <v>Q13 — new service</v>
+        <v>Q28 — security review</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="str">
-        <v>RRR Checklist</v>
+        <v>SIEM / Logging Kickoff</v>
       </c>
       <c r="B35" s="30" t="str">
-        <v>TARC → Development Team</v>
+        <v>TARC</v>
       </c>
       <c r="C35" s="11" t="str">
         <v>Execute</v>
@@ -6592,12 +7048,12 @@
         <v/>
       </c>
       <c r="E35" s="11" t="str">
-        <v>Q13 — new service</v>
+        <v>Q28 — security review</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="17" t="str">
-        <v>Hypercare / Production Readiness</v>
+        <v>Vulnerability Scan &amp; Pen Test</v>
       </c>
       <c r="B36" s="30" t="str">
         <v>TARC</v>
@@ -6609,46 +7065,46 @@
         <v/>
       </c>
       <c r="E36" s="17" t="str">
-        <v>Q13 — new service</v>
+        <v>Q28 — security review</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="str">
-        <v>Quality &amp; Sustainment</v>
-      </c>
-      <c r="B37" s="29" t="str">
-        <v/>
-      </c>
-      <c r="C37" s="29" t="str">
-        <v/>
-      </c>
-      <c r="D37" s="29" t="str">
-        <v/>
-      </c>
-      <c r="E37" s="29" t="str">
-        <v/>
+      <c r="A37" s="11" t="str">
+        <v>Cloud Documentation</v>
+      </c>
+      <c r="B37" s="30" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="C37" s="11" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D37" s="22" t="str">
+        <v/>
+      </c>
+      <c r="E37" s="11" t="str">
+        <v>Q29 — cloud / infra</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="str">
-        <v>Test Strategy</v>
+        <v>Cloud Review</v>
       </c>
       <c r="B38" s="30" t="str">
         <v>TARC</v>
       </c>
       <c r="C38" s="17" t="str">
-        <v>This phase</v>
+        <v>Execute</v>
       </c>
       <c r="D38" s="26" t="str">
         <v/>
       </c>
       <c r="E38" s="17" t="str">
-        <v>Q30 — testing</v>
+        <v>Q29 — cloud / infra</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="str">
-        <v>Operations, Support &amp; M&amp;O Plan</v>
+        <v>TARC</v>
       </c>
       <c r="B39" s="30" t="str">
         <v>TARC</v>
@@ -6660,12 +7116,12 @@
         <v/>
       </c>
       <c r="E39" s="11" t="str">
-        <v>Q31 — support / M&amp;O</v>
+        <v>Q29 — cloud / infra</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="29" t="str">
-        <v>Closeout &amp; Governance</v>
+        <v>Release &amp; Production</v>
       </c>
       <c r="B40" s="29" t="str">
         <v/>
@@ -6682,13 +7138,13 @@
     </row>
     <row r="41">
       <c r="A41" s="11" t="str">
-        <v>Status Reporting</v>
-      </c>
-      <c r="B41" s="31" t="str">
-        <v>PMO</v>
+        <v>Implementation Plan</v>
+      </c>
+      <c r="B41" s="30" t="str">
+        <v>TARC → Development Team</v>
       </c>
       <c r="C41" s="11" t="str">
-        <v>Ongoing</v>
+        <v>Execute</v>
       </c>
       <c r="D41" s="22" t="str">
         <v/>
@@ -6699,115 +7155,319 @@
     </row>
     <row r="42">
       <c r="A42" s="17" t="str">
-        <v>Closeout Report</v>
-      </c>
-      <c r="B42" s="31" t="str">
-        <v>PMO</v>
+        <v>Rollback Plan</v>
+      </c>
+      <c r="B42" s="30" t="str">
+        <v>TARC → Development Team</v>
       </c>
       <c r="C42" s="17" t="str">
-        <v>Close</v>
+        <v>Execute</v>
       </c>
       <c r="D42" s="26" t="str">
         <v/>
       </c>
       <c r="E42" s="17" t="str">
-        <v>Baseline — every project</v>
+        <v>Q13 — new service</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="str">
-        <v>Lessons Learned</v>
-      </c>
-      <c r="B43" s="31" t="str">
-        <v>PMO</v>
+        <v>RFC / RRB</v>
+      </c>
+      <c r="B43" s="30" t="str">
+        <v>TARC → Development Team</v>
       </c>
       <c r="C43" s="11" t="str">
-        <v>Close</v>
+        <v>Execute</v>
       </c>
       <c r="D43" s="22" t="str">
         <v/>
       </c>
       <c r="E43" s="11" t="str">
-        <v>Baseline — every project</v>
+        <v>Q13 — new service</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="str">
+        <v>RRR Checklist</v>
+      </c>
+      <c r="B44" s="30" t="str">
+        <v>TARC → Development Team</v>
+      </c>
+      <c r="C44" s="17" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D44" s="26" t="str">
+        <v/>
+      </c>
+      <c r="E44" s="17" t="str">
+        <v>Q13 — new service</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="11" t="str">
+        <v>Hypercare / Production Readiness</v>
+      </c>
+      <c r="B45" s="30" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="C45" s="11" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D45" s="22" t="str">
+        <v/>
+      </c>
+      <c r="E45" s="11" t="str">
+        <v>Q13 — new service</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="29" t="str">
+        <v>Quality &amp; Sustainment</v>
+      </c>
+      <c r="B46" s="29" t="str">
+        <v/>
+      </c>
+      <c r="C46" s="29" t="str">
+        <v/>
+      </c>
+      <c r="D46" s="29" t="str">
+        <v/>
+      </c>
+      <c r="E46" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="str">
+        <v>Test Strategy</v>
+      </c>
+      <c r="B47" s="30" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="C47" s="11" t="str">
+        <v>This phase</v>
+      </c>
+      <c r="D47" s="22" t="str">
+        <v/>
+      </c>
+      <c r="E47" s="11" t="str">
+        <v>Q30 — testing</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="str">
+        <v>Operations, Support &amp; M&amp;O Plan</v>
+      </c>
+      <c r="B48" s="30" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="C48" s="17" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D48" s="26" t="str">
+        <v/>
+      </c>
+      <c r="E48" s="17" t="str">
+        <v>Q31 — support / M&amp;O</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="29" t="str">
+        <v>Closeout &amp; Governance</v>
+      </c>
+      <c r="B49" s="29" t="str">
+        <v/>
+      </c>
+      <c r="C49" s="29" t="str">
+        <v/>
+      </c>
+      <c r="D49" s="29" t="str">
+        <v/>
+      </c>
+      <c r="E49" s="29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="str">
+        <v>Status Reporting</v>
+      </c>
+      <c r="B50" s="31" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="C50" s="17" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D50" s="26" t="str">
+        <v/>
+      </c>
+      <c r="E50" s="17" t="str">
+        <v>Baseline — every project</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="str">
+        <v>Closeout Report</v>
+      </c>
+      <c r="B51" s="31" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="C51" s="11" t="str">
+        <v>Close</v>
+      </c>
+      <c r="D51" s="22" t="str">
+        <v/>
+      </c>
+      <c r="E51" s="11" t="str">
+        <v>Baseline — every project</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="str">
+        <v>Lessons Learned</v>
+      </c>
+      <c r="B52" s="31" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="C52" s="17" t="str">
+        <v>Close</v>
+      </c>
+      <c r="D52" s="26" t="str">
+        <v/>
+      </c>
+      <c r="E52" s="17" t="str">
+        <v>Baseline — every project</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="str">
         <v>Delegated Approvals</v>
       </c>
-      <c r="B44" s="31" t="str">
+      <c r="B53" s="31" t="str">
         <v>PMO</v>
       </c>
-      <c r="C44" s="17" t="str">
+      <c r="C53" s="11" t="str">
         <v>Ongoing</v>
       </c>
-      <c r="D44" s="26" t="str">
-        <v/>
-      </c>
-      <c r="E44" s="17" t="str">
+      <c r="D53" s="22" t="str">
+        <v/>
+      </c>
+      <c r="E53" s="11" t="str">
         <v>Baseline — every project</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="str">
-        <v/>
-      </c>
-      <c r="B45" s="5" t="str">
-        <v/>
-      </c>
-      <c r="C45" s="5" t="str">
-        <v/>
-      </c>
-      <c r="D45" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E45" s="5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="32" t="str">
+    <row r="54">
+      <c r="A54" s="17" t="str">
+        <v>Project Governance Plan</v>
+      </c>
+      <c r="B54" s="31" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="C54" s="17" t="str">
+        <v>This phase</v>
+      </c>
+      <c r="D54" s="26" t="str">
+        <v>T3</v>
+      </c>
+      <c r="E54" s="17" t="str">
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="str">
+        <v>Governance / Steering-Committee Reporting</v>
+      </c>
+      <c r="B55" s="31" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="C55" s="11" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D55" s="22" t="str">
+        <v>T3</v>
+      </c>
+      <c r="E55" s="11" t="str">
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="str">
+        <v>Post-Implementation Review</v>
+      </c>
+      <c r="B56" s="31" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="C56" s="17" t="str">
+        <v>Close</v>
+      </c>
+      <c r="D56" s="26" t="str">
+        <v>T3</v>
+      </c>
+      <c r="E56" s="17" t="str">
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="str">
+        <v/>
+      </c>
+      <c r="B57" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C57" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D57" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E57" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="str">
         <v>Download the official CA-PMF templates for these artifacts: https://www.capmf.cdt.ca.gov/Templates.html</v>
       </c>
-      <c r="B46" s="5" t="str">
-        <v/>
-      </c>
-      <c r="C46" s="5" t="str">
-        <v/>
-      </c>
-      <c r="D46" s="5" t="str">
-        <v/>
-      </c>
-      <c r="E46" s="5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="str">
-        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 4 of 8   ·   Generated Jul 2, 2026</v>
-      </c>
-      <c r="B48" s="12" t="str">
-        <v/>
-      </c>
-      <c r="C48" s="12" t="str">
-        <v/>
-      </c>
-      <c r="D48" s="12" t="str">
-        <v/>
-      </c>
-      <c r="E48" s="12" t="str">
+      <c r="B58" s="5" t="str">
+        <v/>
+      </c>
+      <c r="C58" s="5" t="str">
+        <v/>
+      </c>
+      <c r="D58" s="5" t="str">
+        <v/>
+      </c>
+      <c r="E58" s="5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="str">
+        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 4 of 8   ·   Generated Jul 6, 2026</v>
+      </c>
+      <c r="B60" s="12" t="str">
+        <v/>
+      </c>
+      <c r="C60" s="12" t="str">
+        <v/>
+      </c>
+      <c r="D60" s="12" t="str">
+        <v/>
+      </c>
+      <c r="E60" s="12" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E60"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7371,7 +8031,7 @@
         <v>This project</v>
       </c>
       <c r="B19" s="50" t="str">
-        <v>Value 84/100 · Complexity 81/100 · Standard (V–C 76)</v>
+        <v>Value 84/100 · Complexity 81/100 · Full (V–C 76)</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -7889,7 +8549,7 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="12" t="str">
-        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 5 of 8   ·   Generated Jul 2, 2026</v>
+        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 5 of 8   ·   Generated Jul 6, 2026</v>
       </c>
       <c r="B38" s="12" t="str">
         <v/>
@@ -7945,7 +8605,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H52"/>
   <cols>
     <col min="1" max="1" width="7.83203125" customWidth="1"/>
     <col min="2" max="2" width="5.83203125" customWidth="1"/>
@@ -8037,7 +8697,7 @@
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="3" t="str">
-        <v>PMO assists / advises  ·  16 deliverables</v>
+        <v>PMO assists / advises  ·  25 deliverables</v>
       </c>
       <c r="B4" s="60" t="str">
         <v/>
@@ -8326,25 +8986,25 @@
         <v>PMO</v>
       </c>
       <c r="B15" s="69" t="str">
-        <v>EXE-17</v>
+        <v>PLN-12</v>
       </c>
       <c r="C15" s="70" t="str">
-        <v>Execute</v>
+        <v>Plan</v>
       </c>
       <c r="D15" s="70" t="str">
-        <v>Completes Lines of Business (LOB )Release Readiness Review (RRR) checklist prior to RRB meeting</v>
+        <v>Risk Management Plan</v>
       </c>
       <c r="E15" s="71" t="str">
         <v>PM</v>
       </c>
       <c r="F15" s="72" t="str">
-        <v/>
+        <v>BA, Sys Own</v>
       </c>
       <c r="G15" s="73" t="str">
-        <v>I: EA</v>
+        <v>I: Sponsor, Steer, BizOwn</v>
       </c>
       <c r="H15" s="74" t="str">
-        <v>Q13</v>
+        <v>Tier 3 — Full governance</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
@@ -8352,25 +9012,25 @@
         <v>PMO</v>
       </c>
       <c r="B16" s="83" t="str">
-        <v>EXE-19</v>
+        <v>PLN-13</v>
       </c>
       <c r="C16" s="82" t="str">
-        <v>Execute</v>
+        <v>Plan</v>
       </c>
       <c r="D16" s="82" t="str">
-        <v>Generate/Update: Product Backlog, Sprint Backlog, Product Increment &amp; Sprint Retrospective/Burndown Chart</v>
+        <v>Quality Management Plan</v>
       </c>
       <c r="E16" s="84" t="str">
-        <v>ScrumM</v>
+        <v>PM</v>
       </c>
       <c r="F16" s="85" t="str">
-        <v>PO, ScrumT</v>
+        <v>ETO, BA</v>
       </c>
       <c r="G16" s="86" t="str">
-        <v>I: Sponsor, ScrumStk</v>
+        <v>I: BizOwn</v>
       </c>
       <c r="H16" s="87" t="str">
-        <v>Q1 (agile)</v>
+        <v>Tier 3 — Full governance</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
@@ -8378,25 +9038,25 @@
         <v>PMO</v>
       </c>
       <c r="B17" s="69" t="str">
-        <v>EXE-20</v>
+        <v>PLN-14</v>
       </c>
       <c r="C17" s="70" t="str">
-        <v>Execute</v>
+        <v>Plan</v>
       </c>
       <c r="D17" s="70" t="str">
-        <v>Create Status Reporting</v>
+        <v>Communications Management Plan</v>
       </c>
       <c r="E17" s="71" t="str">
         <v>PM</v>
       </c>
       <c r="F17" s="72" t="str">
-        <v/>
+        <v>OrgChg</v>
       </c>
       <c r="G17" s="73" t="str">
-        <v>I: EA</v>
+        <v>I: Sponsor, Steer, BizOwn</v>
       </c>
       <c r="H17" s="74" t="str">
-        <v>All projects</v>
+        <v>Tier 3 — Full governance</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
@@ -8404,25 +9064,25 @@
         <v>PMO</v>
       </c>
       <c r="B18" s="83" t="str">
-        <v>CLS-01</v>
+        <v>PLN-15</v>
       </c>
       <c r="C18" s="82" t="str">
-        <v>Close</v>
+        <v>Plan</v>
       </c>
       <c r="D18" s="82" t="str">
-        <v>Create Lessons Learned</v>
+        <v>Change &amp; Schedule Management Plan</v>
       </c>
       <c r="E18" s="84" t="str">
         <v>PM</v>
       </c>
       <c r="F18" s="85" t="str">
-        <v>EA</v>
+        <v>Chg/Rel</v>
       </c>
       <c r="G18" s="86" t="str">
-        <v/>
+        <v>I: Steer</v>
       </c>
       <c r="H18" s="87" t="str">
-        <v>All projects</v>
+        <v>Tier 3 — Full governance</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
@@ -8430,25 +9090,25 @@
         <v>PMO</v>
       </c>
       <c r="B19" s="69" t="str">
-        <v>CLS-02</v>
+        <v>PLN-16</v>
       </c>
       <c r="C19" s="70" t="str">
-        <v>Close</v>
+        <v>Plan</v>
       </c>
       <c r="D19" s="70" t="str">
-        <v>Create Closeout Report</v>
+        <v>Scope Management Plan</v>
       </c>
       <c r="E19" s="71" t="str">
         <v>PM</v>
       </c>
       <c r="F19" s="72" t="str">
-        <v>EA</v>
+        <v>BA, Sys Own</v>
       </c>
       <c r="G19" s="73" t="str">
-        <v/>
+        <v>I: BizOwn</v>
       </c>
       <c r="H19" s="74" t="str">
-        <v>All projects</v>
+        <v>Tier 3 — Full governance</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
@@ -8456,362 +9116,362 @@
         <v>PMO</v>
       </c>
       <c r="B20" s="83" t="str">
+        <v>PLN-17</v>
+      </c>
+      <c r="C20" s="82" t="str">
+        <v>Plan</v>
+      </c>
+      <c r="D20" s="82" t="str">
+        <v>Requirements Management Plan</v>
+      </c>
+      <c r="E20" s="84" t="str">
+        <v>BA</v>
+      </c>
+      <c r="F20" s="85" t="str">
+        <v>PM, Sys Own</v>
+      </c>
+      <c r="G20" s="86" t="str">
+        <v/>
+      </c>
+      <c r="H20" s="87" t="str">
+        <v>Tier 3 — Full governance</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="81" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="B21" s="69" t="str">
+        <v>PLN-18</v>
+      </c>
+      <c r="C21" s="70" t="str">
+        <v>Plan</v>
+      </c>
+      <c r="D21" s="70" t="str">
+        <v>Organization Management Plan</v>
+      </c>
+      <c r="E21" s="71" t="str">
+        <v>PM</v>
+      </c>
+      <c r="F21" s="72" t="str">
+        <v>OrgChg</v>
+      </c>
+      <c r="G21" s="73" t="str">
+        <v>I: BizOwn</v>
+      </c>
+      <c r="H21" s="74" t="str">
+        <v>Tier 3 — Full governance</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="81" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="B22" s="83" t="str">
+        <v>PLN-19</v>
+      </c>
+      <c r="C22" s="82" t="str">
+        <v>Plan</v>
+      </c>
+      <c r="D22" s="82" t="str">
+        <v>Procurement Management Plan</v>
+      </c>
+      <c r="E22" s="84" t="str">
+        <v>Procmt</v>
+      </c>
+      <c r="F22" s="85" t="str">
+        <v>Contr, HW/SW PO</v>
+      </c>
+      <c r="G22" s="86" t="str">
+        <v/>
+      </c>
+      <c r="H22" s="87" t="str">
+        <v>Tier 3 — Full governance</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="81" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="B23" s="69" t="str">
+        <v>PLN-20</v>
+      </c>
+      <c r="C23" s="70" t="str">
+        <v>Plan</v>
+      </c>
+      <c r="D23" s="70" t="str">
+        <v>Cost Management Plan</v>
+      </c>
+      <c r="E23" s="71" t="str">
+        <v>PM</v>
+      </c>
+      <c r="F23" s="72" t="str">
+        <v>Procmt</v>
+      </c>
+      <c r="G23" s="73" t="str">
+        <v/>
+      </c>
+      <c r="H23" s="74" t="str">
+        <v>Tier 3 — Full governance</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="81" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="B24" s="83" t="str">
+        <v>EXE-17</v>
+      </c>
+      <c r="C24" s="82" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D24" s="82" t="str">
+        <v>Completes Lines of Business (LOB )Release Readiness Review (RRR) checklist prior to RRB meeting</v>
+      </c>
+      <c r="E24" s="84" t="str">
+        <v>PM</v>
+      </c>
+      <c r="F24" s="85" t="str">
+        <v/>
+      </c>
+      <c r="G24" s="86" t="str">
+        <v>I: EA</v>
+      </c>
+      <c r="H24" s="87" t="str">
+        <v>Q13</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="81" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="B25" s="69" t="str">
+        <v>EXE-19</v>
+      </c>
+      <c r="C25" s="70" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D25" s="70" t="str">
+        <v>Generate/Update: Product Backlog, Sprint Backlog, Product Increment &amp; Sprint Retrospective/Burndown Chart</v>
+      </c>
+      <c r="E25" s="71" t="str">
+        <v>ScrumM</v>
+      </c>
+      <c r="F25" s="72" t="str">
+        <v>PO, ScrumT</v>
+      </c>
+      <c r="G25" s="73" t="str">
+        <v>I: Sponsor, ScrumStk</v>
+      </c>
+      <c r="H25" s="74" t="str">
+        <v>Q1 (agile)</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="81" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="B26" s="83" t="str">
+        <v>EXE-20</v>
+      </c>
+      <c r="C26" s="82" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D26" s="82" t="str">
+        <v>Create Status Reporting</v>
+      </c>
+      <c r="E26" s="84" t="str">
+        <v>PM</v>
+      </c>
+      <c r="F26" s="85" t="str">
+        <v/>
+      </c>
+      <c r="G26" s="86" t="str">
+        <v>I: EA</v>
+      </c>
+      <c r="H26" s="87" t="str">
+        <v>All projects</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="81" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="B27" s="69" t="str">
+        <v>CLS-01</v>
+      </c>
+      <c r="C27" s="70" t="str">
+        <v>Close</v>
+      </c>
+      <c r="D27" s="70" t="str">
+        <v>Create Lessons Learned</v>
+      </c>
+      <c r="E27" s="71" t="str">
+        <v>PM</v>
+      </c>
+      <c r="F27" s="72" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G27" s="73" t="str">
+        <v/>
+      </c>
+      <c r="H27" s="74" t="str">
+        <v>All projects</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="81" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="B28" s="83" t="str">
+        <v>CLS-02</v>
+      </c>
+      <c r="C28" s="82" t="str">
+        <v>Close</v>
+      </c>
+      <c r="D28" s="82" t="str">
+        <v>Create Closeout Report</v>
+      </c>
+      <c r="E28" s="84" t="str">
+        <v>PM</v>
+      </c>
+      <c r="F28" s="85" t="str">
+        <v>EA</v>
+      </c>
+      <c r="G28" s="86" t="str">
+        <v/>
+      </c>
+      <c r="H28" s="87" t="str">
+        <v>All projects</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="81" t="str">
+        <v>PMO</v>
+      </c>
+      <c r="B29" s="69" t="str">
         <v>CLS-04</v>
       </c>
-      <c r="C20" s="82" t="str">
+      <c r="C29" s="70" t="str">
         <v>Close</v>
       </c>
-      <c r="D20" s="82" t="str">
+      <c r="D29" s="70" t="str">
         <v>Post-Implementation Review (PIR)</v>
       </c>
-      <c r="E20" s="84" t="str">
+      <c r="E29" s="71" t="str">
         <v>PM</v>
       </c>
-      <c r="F20" s="85" t="str">
+      <c r="F29" s="72" t="str">
         <v>Sys Own, BizOwn</v>
       </c>
-      <c r="G20" s="86" t="str">
+      <c r="G29" s="73" t="str">
         <v>I: Sponsor, Steer</v>
       </c>
-      <c r="H20" s="87" t="str">
+      <c r="H29" s="74" t="str">
         <v>Complexity Q23, Q10, Q14, Q17 +6</v>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="88" t="str">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="88" t="str">
         <v>TARC assists / advises  ·  22 deliverables</v>
       </c>
-      <c r="B21" s="89" t="str">
-        <v/>
-      </c>
-      <c r="C21" s="89" t="str">
-        <v/>
-      </c>
-      <c r="D21" s="89" t="str">
-        <v/>
-      </c>
-      <c r="E21" s="89" t="str">
-        <v/>
-      </c>
-      <c r="F21" s="89" t="str">
-        <v/>
-      </c>
-      <c r="G21" s="89" t="str">
-        <v/>
-      </c>
-      <c r="H21" s="89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="90" t="str">
+      <c r="B30" s="89" t="str">
+        <v/>
+      </c>
+      <c r="C30" s="89" t="str">
+        <v/>
+      </c>
+      <c r="D30" s="89" t="str">
+        <v/>
+      </c>
+      <c r="E30" s="89" t="str">
+        <v/>
+      </c>
+      <c r="F30" s="89" t="str">
+        <v/>
+      </c>
+      <c r="G30" s="89" t="str">
+        <v/>
+      </c>
+      <c r="H30" s="89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="90" t="str">
         <v>TARC</v>
       </c>
-      <c r="B22" s="69" t="str">
+      <c r="B31" s="69" t="str">
         <v>INI-06</v>
       </c>
-      <c r="C22" s="70" t="str">
+      <c r="C31" s="70" t="str">
         <v>Initiate</v>
       </c>
-      <c r="D22" s="70" t="str">
+      <c r="D31" s="70" t="str">
         <v>Security Checklist (refer to CSD Cybersecurity Standards in the interim)</v>
       </c>
-      <c r="E22" s="71" t="str">
+      <c r="E31" s="71" t="str">
         <v>Sys Own</v>
       </c>
-      <c r="F22" s="72" t="str">
+      <c r="F31" s="72" t="str">
         <v>CSD Sec, EA, ETO</v>
       </c>
-      <c r="G22" s="73" t="str">
-        <v/>
-      </c>
-      <c r="H22" s="74" t="str">
+      <c r="G31" s="73" t="str">
+        <v/>
+      </c>
+      <c r="H31" s="74" t="str">
         <v>Q28</v>
       </c>
     </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="90" t="str">
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="90" t="str">
         <v>TARC</v>
       </c>
-      <c r="B23" s="83" t="str">
+      <c r="B32" s="83" t="str">
         <v>INI-07</v>
       </c>
-      <c r="C23" s="82" t="str">
+      <c r="C32" s="82" t="str">
         <v>Initiate</v>
       </c>
-      <c r="D23" s="82" t="str">
+      <c r="D32" s="82" t="str">
         <v>Enterprise Architecture Engagement Plan</v>
       </c>
-      <c r="E23" s="84" t="str">
+      <c r="E32" s="84" t="str">
         <v>Sys Own</v>
       </c>
-      <c r="F23" s="85" t="str">
+      <c r="F32" s="85" t="str">
         <v>CSD Sec, EA, ETO</v>
       </c>
-      <c r="G23" s="86" t="str">
-        <v/>
-      </c>
-      <c r="H23" s="87" t="str">
+      <c r="G32" s="86" t="str">
+        <v/>
+      </c>
+      <c r="H32" s="87" t="str">
         <v>All projects</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="91" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="B24" s="69" t="str">
-        <v>PLN-07</v>
-      </c>
-      <c r="C24" s="70" t="str">
-        <v>Plan</v>
-      </c>
-      <c r="D24" s="70" t="str">
-        <v>Create EA-Level Architecture Models and Diagrams</v>
-      </c>
-      <c r="E24" s="71" t="str">
-        <v>EA</v>
-      </c>
-      <c r="F24" s="72" t="str">
-        <v/>
-      </c>
-      <c r="G24" s="73" t="str">
-        <v>I: CSD Sec, Dev Ld, ETO</v>
-      </c>
-      <c r="H24" s="74" t="str">
-        <v>Q29</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="91" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="B25" s="83" t="str">
-        <v>PLN-08</v>
-      </c>
-      <c r="C25" s="82" t="str">
-        <v>Plan</v>
-      </c>
-      <c r="D25" s="82" t="str">
-        <v>Implementation Plan</v>
-      </c>
-      <c r="E25" s="84" t="str">
-        <v>Dev Ld</v>
-      </c>
-      <c r="F25" s="85" t="str">
-        <v>Sys Own, Trans, ETO, OrgChg, BizOwn</v>
-      </c>
-      <c r="G25" s="86" t="str">
-        <v/>
-      </c>
-      <c r="H25" s="87" t="str">
-        <v>Q13</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="91" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="B26" s="69" t="str">
-        <v>PLN-09</v>
-      </c>
-      <c r="C26" s="70" t="str">
-        <v>Plan</v>
-      </c>
-      <c r="D26" s="70" t="str">
-        <v>Rollback Plan</v>
-      </c>
-      <c r="E26" s="71" t="str">
-        <v>Dev Ld</v>
-      </c>
-      <c r="F26" s="72" t="str">
-        <v>PM, Trans, CSD Sec, ETO, Chg/Rel</v>
-      </c>
-      <c r="G26" s="73" t="str">
-        <v/>
-      </c>
-      <c r="H26" s="74" t="str">
-        <v>Q13</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="91" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="B27" s="83" t="str">
-        <v>EXE-01</v>
-      </c>
-      <c r="C27" s="82" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D27" s="82" t="str">
-        <v>Business Impact Analysis (BIA)</v>
-      </c>
-      <c r="E27" s="84" t="str">
-        <v>BizOwn / Sys Own</v>
-      </c>
-      <c r="F27" s="85" t="str">
-        <v>Sys Own, CA Agcy</v>
-      </c>
-      <c r="G27" s="86" t="str">
-        <v>I: CSD Sec</v>
-      </c>
-      <c r="H27" s="87" t="str">
-        <v>Q23</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="91" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="B28" s="69" t="str">
-        <v>EXE-02</v>
-      </c>
-      <c r="C28" s="70" t="str">
-        <v>Initiate</v>
-      </c>
-      <c r="D28" s="70" t="str">
-        <v>Privacy Impact Analysis (PIA)</v>
-      </c>
-      <c r="E28" s="71" t="str">
-        <v>Sys Own</v>
-      </c>
-      <c r="F28" s="72" t="str">
-        <v>PM, CSD Sec, EA, ETO, BizOwn</v>
-      </c>
-      <c r="G28" s="73" t="str">
-        <v/>
-      </c>
-      <c r="H28" s="74" t="str">
-        <v>Q23</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="91" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="B29" s="83" t="str">
-        <v>EXE-03</v>
-      </c>
-      <c r="C29" s="82" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D29" s="82" t="str">
-        <v>Risk Assessment (RA)</v>
-      </c>
-      <c r="E29" s="84" t="str">
-        <v>CSD Sec</v>
-      </c>
-      <c r="F29" s="85" t="str">
-        <v>Sys Own, EA, BizOwn</v>
-      </c>
-      <c r="G29" s="86" t="str">
-        <v>I: PM</v>
-      </c>
-      <c r="H29" s="87" t="str">
-        <v>Q23</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="91" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="B30" s="69" t="str">
-        <v>EXE-04</v>
-      </c>
-      <c r="C30" s="70" t="str">
-        <v>Initiate</v>
-      </c>
-      <c r="D30" s="70" t="str">
-        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
-      </c>
-      <c r="E30" s="71" t="str">
-        <v>Sys Own</v>
-      </c>
-      <c r="F30" s="72" t="str">
-        <v>PM, CSD Sec, EA, ETO</v>
-      </c>
-      <c r="G30" s="73" t="str">
-        <v/>
-      </c>
-      <c r="H30" s="74" t="str">
-        <v>Q23</v>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="91" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="B31" s="83" t="str">
-        <v>EXE-05</v>
-      </c>
-      <c r="C31" s="82" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D31" s="82" t="str">
-        <v>Facilitate Cloud Review</v>
-      </c>
-      <c r="E31" s="84" t="str">
-        <v>Dev Ld</v>
-      </c>
-      <c r="F31" s="85" t="str">
-        <v>EA, CloudArch</v>
-      </c>
-      <c r="G31" s="86" t="str">
-        <v/>
-      </c>
-      <c r="H31" s="87" t="str">
-        <v>Q29</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="91" t="str">
-        <v>TARC</v>
-      </c>
-      <c r="B32" s="69" t="str">
-        <v>EXE-06</v>
-      </c>
-      <c r="C32" s="70" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D32" s="70" t="str">
-        <v>Facilitate TARC Preparation</v>
-      </c>
-      <c r="E32" s="71" t="str">
-        <v>Dev Ld</v>
-      </c>
-      <c r="F32" s="72" t="str">
-        <v>EA, TRT</v>
-      </c>
-      <c r="G32" s="73" t="str">
-        <v/>
-      </c>
-      <c r="H32" s="74" t="str">
-        <v>Q29</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B33" s="83" t="str">
-        <v>EXE-07</v>
-      </c>
-      <c r="C33" s="82" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D33" s="82" t="str">
-        <v>Solution Architecture Document (SAD)</v>
-      </c>
-      <c r="E33" s="84" t="str">
+      <c r="B33" s="69" t="str">
+        <v>PLN-07</v>
+      </c>
+      <c r="C33" s="70" t="str">
+        <v>Plan</v>
+      </c>
+      <c r="D33" s="70" t="str">
+        <v>Create EA-Level Architecture Models and Diagrams</v>
+      </c>
+      <c r="E33" s="71" t="str">
         <v>EA</v>
       </c>
-      <c r="F33" s="85" t="str">
-        <v>CSD Sec, Dev Ld, CloudArch, TARC</v>
-      </c>
-      <c r="G33" s="86" t="str">
-        <v>I: PM</v>
-      </c>
-      <c r="H33" s="87" t="str">
+      <c r="F33" s="72" t="str">
+        <v/>
+      </c>
+      <c r="G33" s="73" t="str">
+        <v>I: CSD Sec, Dev Ld, ETO</v>
+      </c>
+      <c r="H33" s="74" t="str">
         <v>Q29</v>
       </c>
     </row>
@@ -8819,259 +9479,493 @@
       <c r="A34" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B34" s="69" t="str">
-        <v>EXE-08</v>
-      </c>
-      <c r="C34" s="70" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D34" s="70" t="str">
-        <v>SSP Review / Update + Begin Section 3</v>
-      </c>
-      <c r="E34" s="71" t="str">
-        <v>Sys Own</v>
-      </c>
-      <c r="F34" s="72" t="str">
-        <v>PM, CSD Sec</v>
-      </c>
-      <c r="G34" s="73" t="str">
-        <v/>
-      </c>
-      <c r="H34" s="74" t="str">
-        <v>Q23</v>
+      <c r="B34" s="83" t="str">
+        <v>PLN-08</v>
+      </c>
+      <c r="C34" s="82" t="str">
+        <v>Plan</v>
+      </c>
+      <c r="D34" s="82" t="str">
+        <v>Implementation Plan</v>
+      </c>
+      <c r="E34" s="84" t="str">
+        <v>Dev Ld</v>
+      </c>
+      <c r="F34" s="85" t="str">
+        <v>Sys Own, Trans, ETO, OrgChg, BizOwn</v>
+      </c>
+      <c r="G34" s="86" t="str">
+        <v/>
+      </c>
+      <c r="H34" s="87" t="str">
+        <v>Q13</v>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B35" s="83" t="str">
-        <v>EXE-09</v>
-      </c>
-      <c r="C35" s="82" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D35" s="82" t="str">
-        <v>Information System Recovery Plan (ISRP)</v>
-      </c>
-      <c r="E35" s="84" t="str">
+      <c r="B35" s="69" t="str">
+        <v>PLN-09</v>
+      </c>
+      <c r="C35" s="70" t="str">
+        <v>Plan</v>
+      </c>
+      <c r="D35" s="70" t="str">
+        <v>Rollback Plan</v>
+      </c>
+      <c r="E35" s="71" t="str">
         <v>Dev Ld</v>
       </c>
-      <c r="F35" s="85" t="str">
-        <v>PM, BizOwn</v>
-      </c>
-      <c r="G35" s="86" t="str">
-        <v/>
-      </c>
-      <c r="H35" s="87" t="str">
-        <v>Q28</v>
+      <c r="F35" s="72" t="str">
+        <v>PM, Trans, CSD Sec, ETO, Chg/Rel</v>
+      </c>
+      <c r="G35" s="73" t="str">
+        <v/>
+      </c>
+      <c r="H35" s="74" t="str">
+        <v>Q13</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B36" s="69" t="str">
-        <v>EXE-10</v>
-      </c>
-      <c r="C36" s="70" t="str">
+      <c r="B36" s="83" t="str">
+        <v>EXE-01</v>
+      </c>
+      <c r="C36" s="82" t="str">
         <v>Execute</v>
       </c>
-      <c r="D36" s="70" t="str">
-        <v>Security Audit Logging Kick-Off (SIEM)</v>
-      </c>
-      <c r="E36" s="71" t="str">
-        <v>CSD Sec</v>
-      </c>
-      <c r="F36" s="72" t="str">
-        <v/>
-      </c>
-      <c r="G36" s="73" t="str">
-        <v>I: Chg/Rel</v>
-      </c>
-      <c r="H36" s="74" t="str">
-        <v>Q28</v>
+      <c r="D36" s="82" t="str">
+        <v>Business Impact Analysis (BIA)</v>
+      </c>
+      <c r="E36" s="84" t="str">
+        <v>BizOwn / Sys Own</v>
+      </c>
+      <c r="F36" s="85" t="str">
+        <v>Sys Own, CA Agcy</v>
+      </c>
+      <c r="G36" s="86" t="str">
+        <v>I: CSD Sec</v>
+      </c>
+      <c r="H36" s="87" t="str">
+        <v>Q23</v>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B37" s="83" t="str">
-        <v>EXE-11</v>
-      </c>
-      <c r="C37" s="82" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D37" s="82" t="str">
-        <v>Vulnerability Assessment Kick-Off (Nessus / Veracode / Prisma Cloud)</v>
-      </c>
-      <c r="E37" s="84" t="str">
-        <v>PM</v>
-      </c>
-      <c r="F37" s="85" t="str">
-        <v>CSD Sec, Dev Ld, CloudArch</v>
-      </c>
-      <c r="G37" s="86" t="str">
-        <v/>
-      </c>
-      <c r="H37" s="87" t="str">
-        <v>Q28</v>
+      <c r="B37" s="69" t="str">
+        <v>EXE-02</v>
+      </c>
+      <c r="C37" s="70" t="str">
+        <v>Initiate</v>
+      </c>
+      <c r="D37" s="70" t="str">
+        <v>Privacy Impact Analysis (PIA)</v>
+      </c>
+      <c r="E37" s="71" t="str">
+        <v>Sys Own</v>
+      </c>
+      <c r="F37" s="72" t="str">
+        <v>PM, CSD Sec, EA, ETO, BizOwn</v>
+      </c>
+      <c r="G37" s="73" t="str">
+        <v/>
+      </c>
+      <c r="H37" s="74" t="str">
+        <v>Q23</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B38" s="69" t="str">
-        <v>EXE-12</v>
-      </c>
-      <c r="C38" s="70" t="str">
+      <c r="B38" s="83" t="str">
+        <v>EXE-03</v>
+      </c>
+      <c r="C38" s="82" t="str">
         <v>Execute</v>
       </c>
-      <c r="D38" s="70" t="str">
-        <v>System Testing — Vulnerability &amp; Security Scans</v>
-      </c>
-      <c r="E38" s="71" t="str">
-        <v>ETO</v>
-      </c>
-      <c r="F38" s="72" t="str">
-        <v>CSD Sec, Dev Ld</v>
-      </c>
-      <c r="G38" s="73" t="str">
+      <c r="D38" s="82" t="str">
+        <v>Risk Assessment (RA)</v>
+      </c>
+      <c r="E38" s="84" t="str">
+        <v>CSD Sec</v>
+      </c>
+      <c r="F38" s="85" t="str">
+        <v>Sys Own, EA, BizOwn</v>
+      </c>
+      <c r="G38" s="86" t="str">
         <v>I: PM</v>
       </c>
-      <c r="H38" s="74" t="str">
-        <v>Q28</v>
+      <c r="H38" s="87" t="str">
+        <v>Q23</v>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B39" s="83" t="str">
-        <v>EXE-13</v>
-      </c>
-      <c r="C39" s="82" t="str">
-        <v>Execute</v>
-      </c>
-      <c r="D39" s="82" t="str">
-        <v>Application Security Assessment — Penetration Testing</v>
-      </c>
-      <c r="E39" s="84" t="str">
-        <v>CSD Sec</v>
-      </c>
-      <c r="F39" s="85" t="str">
-        <v>ETO</v>
-      </c>
-      <c r="G39" s="86" t="str">
-        <v>I: PM</v>
-      </c>
-      <c r="H39" s="87" t="str">
-        <v>Q28</v>
+      <c r="B39" s="69" t="str">
+        <v>EXE-04</v>
+      </c>
+      <c r="C39" s="70" t="str">
+        <v>Initiate</v>
+      </c>
+      <c r="D39" s="70" t="str">
+        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
+      </c>
+      <c r="E39" s="71" t="str">
+        <v>Sys Own</v>
+      </c>
+      <c r="F39" s="72" t="str">
+        <v>PM, CSD Sec, EA, ETO</v>
+      </c>
+      <c r="G39" s="73" t="str">
+        <v/>
+      </c>
+      <c r="H39" s="74" t="str">
+        <v>Q23</v>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B40" s="69" t="str">
-        <v>EXE-15</v>
-      </c>
-      <c r="C40" s="70" t="str">
+      <c r="B40" s="83" t="str">
+        <v>EXE-05</v>
+      </c>
+      <c r="C40" s="82" t="str">
         <v>Execute</v>
       </c>
-      <c r="D40" s="70" t="str">
-        <v>Schedule and presents RFC for RRB review</v>
-      </c>
-      <c r="E40" s="71" t="str">
+      <c r="D40" s="82" t="str">
+        <v>Facilitate Cloud Review</v>
+      </c>
+      <c r="E40" s="84" t="str">
         <v>Dev Ld</v>
       </c>
-      <c r="F40" s="72" t="str">
-        <v/>
-      </c>
-      <c r="G40" s="73" t="str">
-        <v>R: RRB  ·  I: EA</v>
-      </c>
-      <c r="H40" s="74" t="str">
-        <v>Q13</v>
+      <c r="F40" s="85" t="str">
+        <v>EA, CloudArch</v>
+      </c>
+      <c r="G40" s="86" t="str">
+        <v/>
+      </c>
+      <c r="H40" s="87" t="str">
+        <v>Q29</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B41" s="83" t="str">
-        <v>EXE-16</v>
-      </c>
-      <c r="C41" s="82" t="str">
+      <c r="B41" s="69" t="str">
+        <v>EXE-06</v>
+      </c>
+      <c r="C41" s="70" t="str">
         <v>Execute</v>
       </c>
-      <c r="D41" s="82" t="str">
-        <v>Security Certification &amp; Accreditation (C&amp;A) Package</v>
-      </c>
-      <c r="E41" s="84" t="str">
-        <v>Sys Own</v>
-      </c>
-      <c r="F41" s="85" t="str">
-        <v>CSD Sec</v>
-      </c>
-      <c r="G41" s="86" t="str">
-        <v>I: Sponsor, PM, CloudArch</v>
-      </c>
-      <c r="H41" s="87" t="str">
-        <v>Q28</v>
+      <c r="D41" s="70" t="str">
+        <v>Facilitate TARC Preparation</v>
+      </c>
+      <c r="E41" s="71" t="str">
+        <v>Dev Ld</v>
+      </c>
+      <c r="F41" s="72" t="str">
+        <v>EA, TRT</v>
+      </c>
+      <c r="G41" s="73" t="str">
+        <v/>
+      </c>
+      <c r="H41" s="74" t="str">
+        <v>Q29</v>
       </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B42" s="69" t="str">
-        <v>EXE-18</v>
-      </c>
-      <c r="C42" s="70" t="str">
+      <c r="B42" s="83" t="str">
+        <v>EXE-07</v>
+      </c>
+      <c r="C42" s="82" t="str">
         <v>Execute</v>
       </c>
-      <c r="D42" s="70" t="str">
-        <v>Production Stabilization &amp; Hypercare Period</v>
-      </c>
-      <c r="E42" s="71" t="str">
-        <v>Dev Ld</v>
-      </c>
-      <c r="F42" s="72" t="str">
-        <v>Trans, CSD Sec, Chg/Rel</v>
-      </c>
-      <c r="G42" s="73" t="str">
-        <v>I: Steer, Core, OrgChg, BizOwn</v>
-      </c>
-      <c r="H42" s="74" t="str">
-        <v>Q13</v>
+      <c r="D42" s="82" t="str">
+        <v>Solution Architecture Document (SAD)</v>
+      </c>
+      <c r="E42" s="84" t="str">
+        <v>EA</v>
+      </c>
+      <c r="F42" s="85" t="str">
+        <v>CSD Sec, Dev Ld, CloudArch, TARC</v>
+      </c>
+      <c r="G42" s="86" t="str">
+        <v>I: PM</v>
+      </c>
+      <c r="H42" s="87" t="str">
+        <v>Q29</v>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="91" t="str">
         <v>TARC</v>
       </c>
-      <c r="B43" s="83" t="str">
+      <c r="B43" s="69" t="str">
+        <v>EXE-08</v>
+      </c>
+      <c r="C43" s="70" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D43" s="70" t="str">
+        <v>SSP Review / Update + Begin Section 3</v>
+      </c>
+      <c r="E43" s="71" t="str">
+        <v>Sys Own</v>
+      </c>
+      <c r="F43" s="72" t="str">
+        <v>PM, CSD Sec</v>
+      </c>
+      <c r="G43" s="73" t="str">
+        <v/>
+      </c>
+      <c r="H43" s="74" t="str">
+        <v>Q23</v>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="91" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B44" s="83" t="str">
+        <v>EXE-09</v>
+      </c>
+      <c r="C44" s="82" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D44" s="82" t="str">
+        <v>Information System Recovery Plan (ISRP)</v>
+      </c>
+      <c r="E44" s="84" t="str">
+        <v>Dev Ld</v>
+      </c>
+      <c r="F44" s="85" t="str">
+        <v>PM, BizOwn</v>
+      </c>
+      <c r="G44" s="86" t="str">
+        <v/>
+      </c>
+      <c r="H44" s="87" t="str">
+        <v>Q28</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="91" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B45" s="69" t="str">
+        <v>EXE-10</v>
+      </c>
+      <c r="C45" s="70" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D45" s="70" t="str">
+        <v>Security Audit Logging Kick-Off (SIEM)</v>
+      </c>
+      <c r="E45" s="71" t="str">
+        <v>CSD Sec</v>
+      </c>
+      <c r="F45" s="72" t="str">
+        <v/>
+      </c>
+      <c r="G45" s="73" t="str">
+        <v>I: Chg/Rel</v>
+      </c>
+      <c r="H45" s="74" t="str">
+        <v>Q28</v>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="91" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B46" s="83" t="str">
+        <v>EXE-11</v>
+      </c>
+      <c r="C46" s="82" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D46" s="82" t="str">
+        <v>Vulnerability Assessment Kick-Off (Nessus / Veracode / Prisma Cloud)</v>
+      </c>
+      <c r="E46" s="84" t="str">
+        <v>PM</v>
+      </c>
+      <c r="F46" s="85" t="str">
+        <v>CSD Sec, Dev Ld, CloudArch</v>
+      </c>
+      <c r="G46" s="86" t="str">
+        <v/>
+      </c>
+      <c r="H46" s="87" t="str">
+        <v>Q28</v>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="91" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B47" s="69" t="str">
+        <v>EXE-12</v>
+      </c>
+      <c r="C47" s="70" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D47" s="70" t="str">
+        <v>System Testing — Vulnerability &amp; Security Scans</v>
+      </c>
+      <c r="E47" s="71" t="str">
+        <v>ETO</v>
+      </c>
+      <c r="F47" s="72" t="str">
+        <v>CSD Sec, Dev Ld</v>
+      </c>
+      <c r="G47" s="73" t="str">
+        <v>I: PM</v>
+      </c>
+      <c r="H47" s="74" t="str">
+        <v>Q28</v>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="91" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B48" s="83" t="str">
+        <v>EXE-13</v>
+      </c>
+      <c r="C48" s="82" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D48" s="82" t="str">
+        <v>Application Security Assessment — Penetration Testing</v>
+      </c>
+      <c r="E48" s="84" t="str">
+        <v>CSD Sec</v>
+      </c>
+      <c r="F48" s="85" t="str">
+        <v>ETO</v>
+      </c>
+      <c r="G48" s="86" t="str">
+        <v>I: PM</v>
+      </c>
+      <c r="H48" s="87" t="str">
+        <v>Q28</v>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="91" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B49" s="69" t="str">
+        <v>EXE-15</v>
+      </c>
+      <c r="C49" s="70" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D49" s="70" t="str">
+        <v>Schedule and presents RFC for RRB review</v>
+      </c>
+      <c r="E49" s="71" t="str">
+        <v>Dev Ld</v>
+      </c>
+      <c r="F49" s="72" t="str">
+        <v/>
+      </c>
+      <c r="G49" s="73" t="str">
+        <v>R: RRB  ·  I: EA</v>
+      </c>
+      <c r="H49" s="74" t="str">
+        <v>Q13</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="91" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B50" s="83" t="str">
+        <v>EXE-16</v>
+      </c>
+      <c r="C50" s="82" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D50" s="82" t="str">
+        <v>Security Certification &amp; Accreditation (C&amp;A) Package</v>
+      </c>
+      <c r="E50" s="84" t="str">
+        <v>Sys Own</v>
+      </c>
+      <c r="F50" s="85" t="str">
+        <v>CSD Sec</v>
+      </c>
+      <c r="G50" s="86" t="str">
+        <v>I: Sponsor, PM, CloudArch</v>
+      </c>
+      <c r="H50" s="87" t="str">
+        <v>Q28</v>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="91" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B51" s="69" t="str">
+        <v>EXE-18</v>
+      </c>
+      <c r="C51" s="70" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="D51" s="70" t="str">
+        <v>Production Stabilization &amp; Hypercare Period</v>
+      </c>
+      <c r="E51" s="71" t="str">
+        <v>Dev Ld</v>
+      </c>
+      <c r="F51" s="72" t="str">
+        <v>Trans, CSD Sec, Chg/Rel</v>
+      </c>
+      <c r="G51" s="73" t="str">
+        <v>I: Steer, Core, OrgChg, BizOwn</v>
+      </c>
+      <c r="H51" s="74" t="str">
+        <v>Q13</v>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="91" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B52" s="83" t="str">
         <v>CLS-03</v>
       </c>
-      <c r="C43" s="82" t="str">
+      <c r="C52" s="82" t="str">
         <v>Close</v>
       </c>
-      <c r="D43" s="82" t="str">
+      <c r="D52" s="82" t="str">
         <v xml:space="preserve"> Update EA Repository</v>
       </c>
-      <c r="E43" s="84" t="str">
+      <c r="E52" s="84" t="str">
         <v>EA</v>
       </c>
-      <c r="F43" s="85" t="str">
+      <c r="F52" s="85" t="str">
         <v>PM, Dev Ld, Chg/Rel</v>
       </c>
-      <c r="G43" s="86" t="str">
-        <v/>
-      </c>
-      <c r="H43" s="87" t="str">
+      <c r="G52" s="86" t="str">
+        <v/>
+      </c>
+      <c r="H52" s="87" t="str">
         <v>All projects</v>
       </c>
     </row>
@@ -9080,11 +9974,11 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A30:H30"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H52"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -9475,7 +10369,7 @@
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="12" t="str">
-        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 7 of 8   ·   Generated Jul 2, 2026</v>
+        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 7 of 8   ·   Generated Jul 6, 2026</v>
       </c>
       <c r="B48" s="12" t="str">
         <v/>
@@ -10589,7 +11483,7 @@
     </row>
     <row r="49">
       <c r="A49" s="12" t="str">
-        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 8 of 8   ·   Generated Jul 2, 2026</v>
+        <v>EDD · ESPMO Project Profiler   ·   AB 2123 PFL Expansion   ·   Sheet 8 of 8   ·   Generated Jul 6, 2026</v>
       </c>
       <c r="B49" s="12" t="str">
         <v/>
@@ -10625,7 +11519,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I48"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -11035,36 +11929,36 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="str">
-        <v>Product Vision</v>
+        <v>Project Governance Plan</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v/>
+        <v>Governance_Management_Plan_TEMPLATE.docx</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>Y</v>
       </c>
       <c r="D15" s="2" t="str">
-        <v>Product Vision</v>
+        <v>Project Governance Plan</v>
       </c>
       <c r="E15" s="2" t="str">
         <v>PMO</v>
       </c>
       <c r="F15" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G15" s="2" t="str">
         <v>This phase</v>
       </c>
       <c r="H15" s="2" t="str">
-        <v>Q1 (delivery approach: agile)</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I15" s="2" t="str">
-        <v>PLN-03</v>
+        <v>INI-02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="str">
-        <v>Product Backlog</v>
+        <v>Governance / Steering-Committee Reporting</v>
       </c>
       <c r="B16" s="2" t="str">
         <v/>
@@ -11073,27 +11967,27 @@
         <v>Y</v>
       </c>
       <c r="D16" s="2" t="str">
-        <v>Product Backlog</v>
+        <v>Governance / Steering-Committee Reporting</v>
       </c>
       <c r="E16" s="2" t="str">
         <v>PMO</v>
       </c>
       <c r="F16" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G16" s="2" t="str">
-        <v>This phase</v>
+        <v>Ongoing</v>
       </c>
       <c r="H16" s="2" t="str">
-        <v>Q1 (delivery approach: agile)</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I16" s="2" t="str">
-        <v>EXE-19</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="str">
-        <v>Roadmap / Sprint Planning</v>
+        <v>Risk Management Plan</v>
       </c>
       <c r="B17" s="2" t="str">
         <v/>
@@ -11102,375 +11996,375 @@
         <v>Y</v>
       </c>
       <c r="D17" s="2" t="str">
-        <v>Roadmap / Sprint Planning</v>
+        <v>Risk Management Plan</v>
       </c>
       <c r="E17" s="2" t="str">
         <v>PMO</v>
       </c>
       <c r="F17" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G17" s="2" t="str">
         <v>This phase</v>
       </c>
       <c r="H17" s="2" t="str">
-        <v>Q1 (delivery approach: agile)</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I17" s="2" t="str">
-        <v>PLN-03</v>
+        <v>PLN-12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="str">
-        <v>Rollback Plan</v>
+        <v>Quality Management Plan</v>
       </c>
       <c r="B18" s="2" t="str">
         <v/>
       </c>
       <c r="C18" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D18" s="2" t="str">
-        <v>Rollback Plan</v>
+        <v>Quality Management Plan</v>
       </c>
       <c r="E18" s="2" t="str">
-        <v>TARC → Development Team</v>
+        <v>PMO</v>
       </c>
       <c r="F18" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G18" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="H18" s="2" t="str">
-        <v>Q13 — new service</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I18" s="2" t="str">
-        <v>PLN-09</v>
+        <v>PLN-13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="str">
-        <v>RFC / RRB</v>
+        <v>Communications Management Plan</v>
       </c>
       <c r="B19" s="2" t="str">
         <v/>
       </c>
       <c r="C19" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D19" s="2" t="str">
-        <v>RFC / RRB</v>
+        <v>Communications Management Plan</v>
       </c>
       <c r="E19" s="2" t="str">
-        <v>TARC → Development Team</v>
+        <v>PMO</v>
       </c>
       <c r="F19" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G19" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="H19" s="2" t="str">
-        <v>Q13 — new service</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I19" s="2" t="str">
-        <v>EXE-15</v>
+        <v>PLN-14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="str">
-        <v>RRR Checklist</v>
+        <v>Change &amp; Schedule Management Plan</v>
       </c>
       <c r="B20" s="2" t="str">
         <v/>
       </c>
       <c r="C20" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D20" s="2" t="str">
-        <v>RRR Checklist</v>
+        <v>Change &amp; Schedule Management Plan</v>
       </c>
       <c r="E20" s="2" t="str">
-        <v>TARC → Development Team</v>
+        <v>PMO</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G20" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="H20" s="2" t="str">
-        <v>Q13 — new service</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I20" s="2" t="str">
-        <v>INI-08</v>
+        <v>PLN-15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="str">
-        <v>Hypercare / Production Readiness</v>
+        <v>Scope Management Plan</v>
       </c>
       <c r="B21" s="2" t="str">
         <v/>
       </c>
       <c r="C21" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D21" s="2" t="str">
-        <v>Hypercare / Production Readiness</v>
+        <v>Scope Management Plan</v>
       </c>
       <c r="E21" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G21" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="H21" s="2" t="str">
-        <v>Q13 — new service</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I21" s="2" t="str">
-        <v>EXE-18</v>
+        <v>PLN-16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="str">
-        <v>Privacy Impact Assessment (PIA)</v>
+        <v>Requirements Management Plan</v>
       </c>
       <c r="B22" s="2" t="str">
         <v/>
       </c>
       <c r="C22" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D22" s="2" t="str">
-        <v>Privacy Impact Assessment (PIA)</v>
+        <v>Requirements Management Plan</v>
       </c>
       <c r="E22" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G22" s="2" t="str">
-        <v>Initiate</v>
+        <v>This phase</v>
       </c>
       <c r="H22" s="2" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I22" s="2" t="str">
-        <v>EXE-02</v>
+        <v>PLN-17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="str">
-        <v>Business Impact Analysis (BIA)</v>
+        <v>Organization Management Plan</v>
       </c>
       <c r="B23" s="2" t="str">
         <v/>
       </c>
       <c r="C23" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D23" s="2" t="str">
-        <v>Business Impact Analysis (BIA)</v>
+        <v>Organization Management Plan</v>
       </c>
       <c r="E23" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G23" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="H23" s="2" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I23" s="2" t="str">
-        <v>EXE-01</v>
+        <v>PLN-18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="str">
-        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
+        <v>Procurement Management Plan</v>
       </c>
       <c r="B24" s="2" t="str">
         <v/>
       </c>
       <c r="C24" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D24" s="2" t="str">
-        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
+        <v>Procurement Management Plan</v>
       </c>
       <c r="E24" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="F24" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G24" s="2" t="str">
-        <v>Initiate</v>
+        <v>This phase</v>
       </c>
       <c r="H24" s="2" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I24" s="2" t="str">
-        <v>EXE-04</v>
+        <v>PLN-19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="str">
-        <v>Risk Assessment</v>
+        <v>Cost Management Plan</v>
       </c>
       <c r="B25" s="2" t="str">
         <v/>
       </c>
       <c r="C25" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D25" s="2" t="str">
-        <v>Risk Assessment</v>
+        <v>Cost Management Plan</v>
       </c>
       <c r="E25" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="F25" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G25" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="H25" s="2" t="str">
-        <v>Q23 — sensitive data</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I25" s="2" t="str">
-        <v>EXE-03</v>
+        <v>PLN-20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="str">
-        <v>C&amp;A Package</v>
+        <v>Post-Implementation Review</v>
       </c>
       <c r="B26" s="2" t="str">
         <v/>
       </c>
       <c r="C26" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D26" s="2" t="str">
-        <v>C&amp;A Package</v>
+        <v>Post-Implementation Review</v>
       </c>
       <c r="E26" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v/>
+        <v>T3</v>
       </c>
       <c r="G26" s="2" t="str">
-        <v>Execute</v>
+        <v>Close</v>
       </c>
       <c r="H26" s="2" t="str">
-        <v>Q28 — security review</v>
+        <v>Complexity tier — driven by Q23, Q10, Q14, Q17 +6 more (incl. Q23 data floor)</v>
       </c>
       <c r="I26" s="2" t="str">
-        <v>EXE-16</v>
+        <v>CLS-04</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="str">
-        <v>ISRP</v>
+        <v>Product Vision</v>
       </c>
       <c r="B27" s="2" t="str">
         <v/>
       </c>
       <c r="C27" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D27" s="2" t="str">
-        <v>ISRP</v>
+        <v>Product Vision</v>
       </c>
       <c r="E27" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="F27" s="2" t="str">
         <v/>
       </c>
       <c r="G27" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="H27" s="2" t="str">
-        <v>Q28 — security review</v>
+        <v>Q1 (delivery approach: agile)</v>
       </c>
       <c r="I27" s="2" t="str">
-        <v>EXE-09</v>
+        <v>PLN-03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="str">
-        <v>SIEM / Logging Kickoff</v>
+        <v>Product Backlog</v>
       </c>
       <c r="B28" s="2" t="str">
         <v/>
       </c>
       <c r="C28" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D28" s="2" t="str">
-        <v>SIEM / Logging Kickoff</v>
+        <v>Product Backlog</v>
       </c>
       <c r="E28" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="F28" s="2" t="str">
         <v/>
       </c>
       <c r="G28" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="H28" s="2" t="str">
-        <v>Q28 — security review</v>
+        <v>Q1 (delivery approach: agile)</v>
       </c>
       <c r="I28" s="2" t="str">
-        <v>EXE-10</v>
+        <v>EXE-19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="str">
-        <v>Vulnerability Scan &amp; Pen Test</v>
+        <v>Roadmap / Sprint Planning</v>
       </c>
       <c r="B29" s="2" t="str">
         <v/>
       </c>
       <c r="C29" s="2" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
       <c r="D29" s="2" t="str">
-        <v>Vulnerability Scan &amp; Pen Test</v>
+        <v>Roadmap / Sprint Planning</v>
       </c>
       <c r="E29" s="2" t="str">
-        <v>TARC</v>
+        <v>PMO</v>
       </c>
       <c r="F29" s="2" t="str">
         <v/>
       </c>
       <c r="G29" s="2" t="str">
-        <v>Execute</v>
+        <v>This phase</v>
       </c>
       <c r="H29" s="2" t="str">
-        <v>Q28 — security review</v>
+        <v>Q1 (delivery approach: agile)</v>
       </c>
       <c r="I29" s="2" t="str">
-        <v>EXE-11</v>
+        <v>PLN-03</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="str">
-        <v>Cloud Architecture Diagram</v>
+        <v>Rollback Plan</v>
       </c>
       <c r="B30" s="2" t="str">
         <v/>
@@ -11479,27 +12373,27 @@
         <v>N</v>
       </c>
       <c r="D30" s="2" t="str">
-        <v>Cloud Architecture Diagram</v>
+        <v>Rollback Plan</v>
       </c>
       <c r="E30" s="2" t="str">
-        <v>TARC</v>
+        <v>TARC → Development Team</v>
       </c>
       <c r="F30" s="2" t="str">
         <v/>
       </c>
       <c r="G30" s="2" t="str">
-        <v>This phase</v>
+        <v>Execute</v>
       </c>
       <c r="H30" s="2" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q13 — new service</v>
       </c>
       <c r="I30" s="2" t="str">
-        <v/>
+        <v>PLN-09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="str">
-        <v>Cloud Documentation</v>
+        <v>RFC / RRB</v>
       </c>
       <c r="B31" s="2" t="str">
         <v/>
@@ -11508,10 +12402,10 @@
         <v>N</v>
       </c>
       <c r="D31" s="2" t="str">
-        <v>Cloud Documentation</v>
+        <v>RFC / RRB</v>
       </c>
       <c r="E31" s="2" t="str">
-        <v>TARC</v>
+        <v>TARC → Development Team</v>
       </c>
       <c r="F31" s="2" t="str">
         <v/>
@@ -11520,15 +12414,15 @@
         <v>Execute</v>
       </c>
       <c r="H31" s="2" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q13 — new service</v>
       </c>
       <c r="I31" s="2" t="str">
-        <v/>
+        <v>EXE-15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="str">
-        <v>Cloud Review</v>
+        <v>RRR Checklist</v>
       </c>
       <c r="B32" s="2" t="str">
         <v/>
@@ -11537,10 +12431,10 @@
         <v>N</v>
       </c>
       <c r="D32" s="2" t="str">
-        <v>Cloud Review</v>
+        <v>RRR Checklist</v>
       </c>
       <c r="E32" s="2" t="str">
-        <v>TARC</v>
+        <v>TARC → Development Team</v>
       </c>
       <c r="F32" s="2" t="str">
         <v/>
@@ -11549,15 +12443,15 @@
         <v>Execute</v>
       </c>
       <c r="H32" s="2" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q13 — new service</v>
       </c>
       <c r="I32" s="2" t="str">
-        <v>EXE-05</v>
+        <v>INI-08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="str">
-        <v>TARC</v>
+        <v>Hypercare / Production Readiness</v>
       </c>
       <c r="B33" s="2" t="str">
         <v/>
@@ -11566,7 +12460,7 @@
         <v>N</v>
       </c>
       <c r="D33" s="2" t="str">
-        <v>TARC</v>
+        <v>Hypercare / Production Readiness</v>
       </c>
       <c r="E33" s="2" t="str">
         <v>TARC</v>
@@ -11578,15 +12472,15 @@
         <v>Execute</v>
       </c>
       <c r="H33" s="2" t="str">
-        <v>Q29 — cloud / infra</v>
+        <v>Q13 — new service</v>
       </c>
       <c r="I33" s="2" t="str">
-        <v>EXE-06</v>
+        <v>EXE-18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="str">
-        <v>Vendor SOW &amp; Contract Oversight</v>
+        <v>Privacy Impact Assessment (PIA)</v>
       </c>
       <c r="B34" s="2" t="str">
         <v/>
@@ -11595,27 +12489,27 @@
         <v>N</v>
       </c>
       <c r="D34" s="2" t="str">
-        <v>Vendor SOW &amp; Contract Oversight</v>
+        <v>Privacy Impact Assessment (PIA)</v>
       </c>
       <c r="E34" s="2" t="str">
-        <v>TARC → TGD — Procurement</v>
+        <v>TARC</v>
       </c>
       <c r="F34" s="2" t="str">
         <v/>
       </c>
       <c r="G34" s="2" t="str">
-        <v>This phase</v>
+        <v>Initiate</v>
       </c>
       <c r="H34" s="2" t="str">
-        <v>Q18 — vendor-delivered</v>
+        <v>Q23 — sensitive data</v>
       </c>
       <c r="I34" s="2" t="str">
-        <v/>
+        <v>EXE-02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="str">
-        <v>Test Strategy</v>
+        <v>Business Impact Analysis (BIA)</v>
       </c>
       <c r="B35" s="2" t="str">
         <v/>
@@ -11624,7 +12518,7 @@
         <v>N</v>
       </c>
       <c r="D35" s="2" t="str">
-        <v>Test Strategy</v>
+        <v>Business Impact Analysis (BIA)</v>
       </c>
       <c r="E35" s="2" t="str">
         <v>TARC</v>
@@ -11633,18 +12527,18 @@
         <v/>
       </c>
       <c r="G35" s="2" t="str">
-        <v>This phase</v>
+        <v>Execute</v>
       </c>
       <c r="H35" s="2" t="str">
-        <v>Q30 — testing</v>
+        <v>Q23 — sensitive data</v>
       </c>
       <c r="I35" s="2" t="str">
-        <v/>
+        <v>EXE-01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="str">
-        <v>Operations, Support &amp; M&amp;O Plan</v>
+        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
       </c>
       <c r="B36" s="2" t="str">
         <v/>
@@ -11653,7 +12547,7 @@
         <v>N</v>
       </c>
       <c r="D36" s="2" t="str">
-        <v>Operations, Support &amp; M&amp;O Plan</v>
+        <v>System Security Plan (SSP) — Initial (Sections 1 &amp; 2)</v>
       </c>
       <c r="E36" s="2" t="str">
         <v>TARC</v>
@@ -11662,19 +12556,367 @@
         <v/>
       </c>
       <c r="G36" s="2" t="str">
+        <v>Initiate</v>
+      </c>
+      <c r="H36" s="2" t="str">
+        <v>Q23 — sensitive data</v>
+      </c>
+      <c r="I36" s="2" t="str">
+        <v>EXE-04</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="str">
+        <v>Risk Assessment</v>
+      </c>
+      <c r="B37" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C37" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <v>Risk Assessment</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F37" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str">
         <v>Execute</v>
       </c>
-      <c r="H36" s="2" t="str">
+      <c r="H37" s="2" t="str">
+        <v>Q23 — sensitive data</v>
+      </c>
+      <c r="I37" s="2" t="str">
+        <v>EXE-03</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="str">
+        <v>C&amp;A Package</v>
+      </c>
+      <c r="B38" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C38" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <v>C&amp;A Package</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G38" s="2" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="H38" s="2" t="str">
+        <v>Q28 — security review</v>
+      </c>
+      <c r="I38" s="2" t="str">
+        <v>EXE-16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="str">
+        <v>ISRP</v>
+      </c>
+      <c r="B39" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C39" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <v>ISRP</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F39" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="H39" s="2" t="str">
+        <v>Q28 — security review</v>
+      </c>
+      <c r="I39" s="2" t="str">
+        <v>EXE-09</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="str">
+        <v>SIEM / Logging Kickoff</v>
+      </c>
+      <c r="B40" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C40" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <v>SIEM / Logging Kickoff</v>
+      </c>
+      <c r="E40" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F40" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="H40" s="2" t="str">
+        <v>Q28 — security review</v>
+      </c>
+      <c r="I40" s="2" t="str">
+        <v>EXE-10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="str">
+        <v>Vulnerability Scan &amp; Pen Test</v>
+      </c>
+      <c r="B41" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C41" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <v>Vulnerability Scan &amp; Pen Test</v>
+      </c>
+      <c r="E41" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F41" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="H41" s="2" t="str">
+        <v>Q28 — security review</v>
+      </c>
+      <c r="I41" s="2" t="str">
+        <v>EXE-11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="str">
+        <v>Cloud Architecture Diagram</v>
+      </c>
+      <c r="B42" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C42" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <v>Cloud Architecture Diagram</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F42" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v>This phase</v>
+      </c>
+      <c r="H42" s="2" t="str">
+        <v>Q29 — cloud / infra</v>
+      </c>
+      <c r="I42" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="str">
+        <v>Cloud Documentation</v>
+      </c>
+      <c r="B43" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C43" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <v>Cloud Documentation</v>
+      </c>
+      <c r="E43" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F43" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="H43" s="2" t="str">
+        <v>Q29 — cloud / infra</v>
+      </c>
+      <c r="I43" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="str">
+        <v>Cloud Review</v>
+      </c>
+      <c r="B44" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C44" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <v>Cloud Review</v>
+      </c>
+      <c r="E44" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F44" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="H44" s="2" t="str">
+        <v>Q29 — cloud / infra</v>
+      </c>
+      <c r="I44" s="2" t="str">
+        <v>EXE-05</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="B45" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C45" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="E45" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F45" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="H45" s="2" t="str">
+        <v>Q29 — cloud / infra</v>
+      </c>
+      <c r="I45" s="2" t="str">
+        <v>EXE-06</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="str">
+        <v>Vendor SOW &amp; Contract Oversight</v>
+      </c>
+      <c r="B46" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C46" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D46" s="2" t="str">
+        <v>Vendor SOW &amp; Contract Oversight</v>
+      </c>
+      <c r="E46" s="2" t="str">
+        <v>TARC → TGD — Procurement</v>
+      </c>
+      <c r="F46" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str">
+        <v>This phase</v>
+      </c>
+      <c r="H46" s="2" t="str">
+        <v>Q18 — vendor-delivered</v>
+      </c>
+      <c r="I46" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="str">
+        <v>Test Strategy</v>
+      </c>
+      <c r="B47" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C47" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D47" s="2" t="str">
+        <v>Test Strategy</v>
+      </c>
+      <c r="E47" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F47" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v>This phase</v>
+      </c>
+      <c r="H47" s="2" t="str">
+        <v>Q30 — testing</v>
+      </c>
+      <c r="I47" s="2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="str">
+        <v>Operations, Support &amp; M&amp;O Plan</v>
+      </c>
+      <c r="B48" s="2" t="str">
+        <v/>
+      </c>
+      <c r="C48" s="2" t="str">
+        <v>N</v>
+      </c>
+      <c r="D48" s="2" t="str">
+        <v>Operations, Support &amp; M&amp;O Plan</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <v>TARC</v>
+      </c>
+      <c r="F48" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str">
+        <v>Execute</v>
+      </c>
+      <c r="H48" s="2" t="str">
         <v>Q31 — support / M&amp;O</v>
       </c>
-      <c r="I36" s="2" t="str">
+      <c r="I48" s="2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I48"/>
   </ignoredErrors>
 </worksheet>
 </file>